--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -14,7 +14,9 @@
     <sheet name="By Policy Type" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="By Expiry Month" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'All Policies'!$A$1:$M$316</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -22,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +32,22 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001E3A5F"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,8 +62,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -422,67 +436,67 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>source_file</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>vehicle_chassis_number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>insurance_company_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>policy_number</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>od_start_date</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>od_end_date</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>fire_covered</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>damage_coverage</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>premium_amount</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>days_left</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>policy_duration</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>policy_type</t>
         </is>
@@ -532,13 +546,13 @@
       <c r="I2" t="n">
         <v>1517</v>
       </c>
-      <c r="J2" t="n">
-        <v>328</v>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J2">
+        <f>IF(F2="","",IFERROR(INT(F2-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K2">
+        <f>IF(J2="","",IF(J2&lt;0,"Expired",IF(J2&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L2" t="n">
         <v>1</v>
@@ -593,13 +607,13 @@
       <c r="I3" t="n">
         <v>1517</v>
       </c>
-      <c r="J3" t="n">
-        <v>328</v>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J3">
+        <f>IF(F3="","",IFERROR(INT(F3-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K3">
+        <f>IF(J3="","",IF(J3&lt;0,"Expired",IF(J3&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L3" t="n">
         <v>1</v>
@@ -654,13 +668,13 @@
       <c r="I4" t="n">
         <v>1517</v>
       </c>
-      <c r="J4" t="n">
-        <v>328</v>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J4">
+        <f>IF(F4="","",IFERROR(INT(F4-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K4">
+        <f>IF(J4="","",IF(J4&lt;0,"Expired",IF(J4&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L4" t="n">
         <v>1</v>
@@ -715,13 +729,13 @@
       <c r="I5" t="n">
         <v>1517</v>
       </c>
-      <c r="J5" t="n">
-        <v>328</v>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J5">
+        <f>IF(F5="","",IFERROR(INT(F5-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K5">
+        <f>IF(J5="","",IF(J5&lt;0,"Expired",IF(J5&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -776,13 +790,13 @@
       <c r="I6" t="n">
         <v>1517</v>
       </c>
-      <c r="J6" t="n">
-        <v>328</v>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J6">
+        <f>IF(F6="","",IFERROR(INT(F6-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K6">
+        <f>IF(J6="","",IF(J6&lt;0,"Expired",IF(J6&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -837,13 +851,13 @@
       <c r="I7" t="n">
         <v>1517</v>
       </c>
-      <c r="J7" t="n">
-        <v>328</v>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J7">
+        <f>IF(F7="","",IFERROR(INT(F7-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K7">
+        <f>IF(J7="","",IF(J7&lt;0,"Expired",IF(J7&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -898,13 +912,13 @@
       <c r="I8" t="n">
         <v>1517</v>
       </c>
-      <c r="J8" t="n">
-        <v>329</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J8">
+        <f>IF(F8="","",IFERROR(INT(F8-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K8">
+        <f>IF(J8="","",IF(J8&lt;0,"Expired",IF(J8&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -959,13 +973,13 @@
       <c r="I9" t="n">
         <v>1517</v>
       </c>
-      <c r="J9" t="n">
-        <v>329</v>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J9">
+        <f>IF(F9="","",IFERROR(INT(F9-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K9">
+        <f>IF(J9="","",IF(J9&lt;0,"Expired",IF(J9&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1020,13 +1034,13 @@
       <c r="I10" t="n">
         <v>1517</v>
       </c>
-      <c r="J10" t="n">
-        <v>329</v>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J10">
+        <f>IF(F10="","",IFERROR(INT(F10-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K10">
+        <f>IF(J10="","",IF(J10&lt;0,"Expired",IF(J10&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1081,13 +1095,13 @@
       <c r="I11" t="n">
         <v>1517</v>
       </c>
-      <c r="J11" t="n">
-        <v>329</v>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J11">
+        <f>IF(F11="","",IFERROR(INT(F11-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K11">
+        <f>IF(J11="","",IF(J11&lt;0,"Expired",IF(J11&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L11" t="n">
         <v>1</v>
@@ -1142,13 +1156,13 @@
       <c r="I12" t="n">
         <v>1517</v>
       </c>
-      <c r="J12" t="n">
-        <v>329</v>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J12">
+        <f>IF(F12="","",IFERROR(INT(F12-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K12">
+        <f>IF(J12="","",IF(J12&lt;0,"Expired",IF(J12&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L12" t="n">
         <v>1</v>
@@ -1203,13 +1217,13 @@
       <c r="I13" t="n">
         <v>1517</v>
       </c>
-      <c r="J13" t="n">
-        <v>329</v>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J13">
+        <f>IF(F13="","",IFERROR(INT(F13-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K13">
+        <f>IF(J13="","",IF(J13&lt;0,"Expired",IF(J13&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1264,13 +1278,13 @@
       <c r="I14" t="n">
         <v>2384</v>
       </c>
-      <c r="J14" t="n">
-        <v>270</v>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J14">
+        <f>IF(F14="","",IFERROR(INT(F14-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K14">
+        <f>IF(J14="","",IF(J14&lt;0,"Expired",IF(J14&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L14" t="n">
         <v>1</v>
@@ -1325,13 +1339,13 @@
       <c r="I15" t="n">
         <v>3391</v>
       </c>
-      <c r="J15" t="n">
-        <v>144</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J15">
+        <f>IF(F15="","",IFERROR(INT(F15-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K15">
+        <f>IF(J15="","",IF(J15&lt;0,"Expired",IF(J15&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L15" t="n">
         <v>1</v>
@@ -1386,13 +1400,13 @@
       <c r="I16" t="n">
         <v>3391</v>
       </c>
-      <c r="J16" t="n">
-        <v>152</v>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J16">
+        <f>IF(F16="","",IFERROR(INT(F16-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K16">
+        <f>IF(J16="","",IF(J16&lt;0,"Expired",IF(J16&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1447,13 +1461,13 @@
       <c r="I17" t="n">
         <v>3391</v>
       </c>
-      <c r="J17" t="n">
-        <v>152</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J17">
+        <f>IF(F17="","",IFERROR(INT(F17-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K17">
+        <f>IF(J17="","",IF(J17&lt;0,"Expired",IF(J17&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L17" t="n">
         <v>1</v>
@@ -1508,13 +1522,13 @@
       <c r="I18" t="n">
         <v>3391</v>
       </c>
-      <c r="J18" t="n">
-        <v>152</v>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J18">
+        <f>IF(F18="","",IFERROR(INT(F18-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K18">
+        <f>IF(J18="","",IF(J18&lt;0,"Expired",IF(J18&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L18" t="n">
         <v>1</v>
@@ -1569,13 +1583,13 @@
       <c r="I19" t="n">
         <v>3391</v>
       </c>
-      <c r="J19" t="n">
-        <v>152</v>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J19">
+        <f>IF(F19="","",IFERROR(INT(F19-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K19">
+        <f>IF(J19="","",IF(J19&lt;0,"Expired",IF(J19&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L19" t="n">
         <v>1</v>
@@ -1630,13 +1644,13 @@
       <c r="I20" t="n">
         <v>3391</v>
       </c>
-      <c r="J20" t="n">
-        <v>152</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J20">
+        <f>IF(F20="","",IFERROR(INT(F20-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K20">
+        <f>IF(J20="","",IF(J20&lt;0,"Expired",IF(J20&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L20" t="n">
         <v>1</v>
@@ -1691,13 +1705,13 @@
       <c r="I21" t="n">
         <v>3391</v>
       </c>
-      <c r="J21" t="n">
-        <v>152</v>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J21">
+        <f>IF(F21="","",IFERROR(INT(F21-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K21">
+        <f>IF(J21="","",IF(J21&lt;0,"Expired",IF(J21&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L21" t="n">
         <v>1</v>
@@ -1752,13 +1766,13 @@
       <c r="I22" t="n">
         <v>3391</v>
       </c>
-      <c r="J22" t="n">
-        <v>152</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J22">
+        <f>IF(F22="","",IFERROR(INT(F22-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K22">
+        <f>IF(J22="","",IF(J22&lt;0,"Expired",IF(J22&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L22" t="n">
         <v>1</v>
@@ -1813,13 +1827,13 @@
       <c r="I23" t="n">
         <v>3391</v>
       </c>
-      <c r="J23" t="n">
-        <v>152</v>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J23">
+        <f>IF(F23="","",IFERROR(INT(F23-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K23">
+        <f>IF(J23="","",IF(J23&lt;0,"Expired",IF(J23&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L23" t="n">
         <v>1</v>
@@ -1874,13 +1888,13 @@
       <c r="I24" t="n">
         <v>3391</v>
       </c>
-      <c r="J24" t="n">
-        <v>152</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J24">
+        <f>IF(F24="","",IFERROR(INT(F24-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K24">
+        <f>IF(J24="","",IF(J24&lt;0,"Expired",IF(J24&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L24" t="n">
         <v>1</v>
@@ -1935,13 +1949,13 @@
       <c r="I25" t="n">
         <v>3391</v>
       </c>
-      <c r="J25" t="n">
-        <v>152</v>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J25">
+        <f>IF(F25="","",IFERROR(INT(F25-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K25">
+        <f>IF(J25="","",IF(J25&lt;0,"Expired",IF(J25&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L25" t="n">
         <v>1</v>
@@ -1996,13 +2010,13 @@
       <c r="I26" t="n">
         <v>3391</v>
       </c>
-      <c r="J26" t="n">
-        <v>152</v>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J26">
+        <f>IF(F26="","",IFERROR(INT(F26-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K26">
+        <f>IF(J26="","",IF(J26&lt;0,"Expired",IF(J26&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L26" t="n">
         <v>1</v>
@@ -2057,13 +2071,13 @@
       <c r="I27" t="n">
         <v>3391</v>
       </c>
-      <c r="J27" t="n">
-        <v>152</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J27">
+        <f>IF(F27="","",IFERROR(INT(F27-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K27">
+        <f>IF(J27="","",IF(J27&lt;0,"Expired",IF(J27&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L27" t="n">
         <v>1</v>
@@ -2118,13 +2132,13 @@
       <c r="I28" t="n">
         <v>3391</v>
       </c>
-      <c r="J28" t="n">
-        <v>152</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J28">
+        <f>IF(F28="","",IFERROR(INT(F28-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K28">
+        <f>IF(J28="","",IF(J28&lt;0,"Expired",IF(J28&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L28" t="n">
         <v>1</v>
@@ -2179,13 +2193,13 @@
       <c r="I29" t="n">
         <v>3391</v>
       </c>
-      <c r="J29" t="n">
-        <v>152</v>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J29">
+        <f>IF(F29="","",IFERROR(INT(F29-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K29">
+        <f>IF(J29="","",IF(J29&lt;0,"Expired",IF(J29&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L29" t="n">
         <v>1</v>
@@ -2240,13 +2254,13 @@
       <c r="I30" t="n">
         <v>3391</v>
       </c>
-      <c r="J30" t="n">
-        <v>152</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J30">
+        <f>IF(F30="","",IFERROR(INT(F30-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K30">
+        <f>IF(J30="","",IF(J30&lt;0,"Expired",IF(J30&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L30" t="n">
         <v>1</v>
@@ -2301,13 +2315,13 @@
       <c r="I31" t="n">
         <v>3391</v>
       </c>
-      <c r="J31" t="n">
-        <v>152</v>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J31">
+        <f>IF(F31="","",IFERROR(INT(F31-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K31">
+        <f>IF(J31="","",IF(J31&lt;0,"Expired",IF(J31&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L31" t="n">
         <v>1</v>
@@ -2362,13 +2376,13 @@
       <c r="I32" t="n">
         <v>3391</v>
       </c>
-      <c r="J32" t="n">
-        <v>152</v>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J32">
+        <f>IF(F32="","",IFERROR(INT(F32-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K32">
+        <f>IF(J32="","",IF(J32&lt;0,"Expired",IF(J32&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L32" t="n">
         <v>1</v>
@@ -2423,13 +2437,13 @@
       <c r="I33" t="n">
         <v>3391</v>
       </c>
-      <c r="J33" t="n">
-        <v>152</v>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J33">
+        <f>IF(F33="","",IFERROR(INT(F33-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K33">
+        <f>IF(J33="","",IF(J33&lt;0,"Expired",IF(J33&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L33" t="n">
         <v>1</v>
@@ -2484,13 +2498,13 @@
       <c r="I34" t="n">
         <v>3391</v>
       </c>
-      <c r="J34" t="n">
-        <v>152</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J34">
+        <f>IF(F34="","",IFERROR(INT(F34-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K34">
+        <f>IF(J34="","",IF(J34&lt;0,"Expired",IF(J34&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L34" t="n">
         <v>1</v>
@@ -2545,13 +2559,13 @@
       <c r="I35" t="n">
         <v>3391</v>
       </c>
-      <c r="J35" t="n">
-        <v>152</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J35">
+        <f>IF(F35="","",IFERROR(INT(F35-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K35">
+        <f>IF(J35="","",IF(J35&lt;0,"Expired",IF(J35&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L35" t="n">
         <v>1</v>
@@ -2606,13 +2620,13 @@
       <c r="I36" t="n">
         <v>3391</v>
       </c>
-      <c r="J36" t="n">
-        <v>152</v>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J36">
+        <f>IF(F36="","",IFERROR(INT(F36-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K36">
+        <f>IF(J36="","",IF(J36&lt;0,"Expired",IF(J36&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2667,13 +2681,13 @@
       <c r="I37" t="n">
         <v>3391</v>
       </c>
-      <c r="J37" t="n">
-        <v>152</v>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J37">
+        <f>IF(F37="","",IFERROR(INT(F37-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K37">
+        <f>IF(J37="","",IF(J37&lt;0,"Expired",IF(J37&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -2728,13 +2742,13 @@
       <c r="I38" t="n">
         <v>3391</v>
       </c>
-      <c r="J38" t="n">
-        <v>152</v>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J38">
+        <f>IF(F38="","",IFERROR(INT(F38-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K38">
+        <f>IF(J38="","",IF(J38&lt;0,"Expired",IF(J38&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L38" t="n">
         <v>1</v>
@@ -2789,13 +2803,13 @@
       <c r="I39" t="n">
         <v>3391</v>
       </c>
-      <c r="J39" t="n">
-        <v>153</v>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J39">
+        <f>IF(F39="","",IFERROR(INT(F39-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K39">
+        <f>IF(J39="","",IF(J39&lt;0,"Expired",IF(J39&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L39" t="n">
         <v>1</v>
@@ -2850,13 +2864,13 @@
       <c r="I40" t="n">
         <v>3391</v>
       </c>
-      <c r="J40" t="n">
-        <v>153</v>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J40">
+        <f>IF(F40="","",IFERROR(INT(F40-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K40">
+        <f>IF(J40="","",IF(J40&lt;0,"Expired",IF(J40&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L40" t="n">
         <v>1</v>
@@ -2911,13 +2925,13 @@
       <c r="I41" t="n">
         <v>3391</v>
       </c>
-      <c r="J41" t="n">
-        <v>153</v>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J41">
+        <f>IF(F41="","",IFERROR(INT(F41-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K41">
+        <f>IF(J41="","",IF(J41&lt;0,"Expired",IF(J41&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L41" t="n">
         <v>1</v>
@@ -2972,13 +2986,13 @@
       <c r="I42" t="n">
         <v>3391</v>
       </c>
-      <c r="J42" t="n">
-        <v>153</v>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J42">
+        <f>IF(F42="","",IFERROR(INT(F42-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K42">
+        <f>IF(J42="","",IF(J42&lt;0,"Expired",IF(J42&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L42" t="n">
         <v>1</v>
@@ -3033,13 +3047,13 @@
       <c r="I43" t="n">
         <v>3391</v>
       </c>
-      <c r="J43" t="n">
-        <v>153</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J43">
+        <f>IF(F43="","",IFERROR(INT(F43-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K43">
+        <f>IF(J43="","",IF(J43&lt;0,"Expired",IF(J43&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L43" t="n">
         <v>1</v>
@@ -3094,13 +3108,13 @@
       <c r="I44" t="n">
         <v>3391</v>
       </c>
-      <c r="J44" t="n">
-        <v>153</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J44">
+        <f>IF(F44="","",IFERROR(INT(F44-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K44">
+        <f>IF(J44="","",IF(J44&lt;0,"Expired",IF(J44&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L44" t="n">
         <v>1</v>
@@ -3155,13 +3169,13 @@
       <c r="I45" t="n">
         <v>3391</v>
       </c>
-      <c r="J45" t="n">
-        <v>153</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J45">
+        <f>IF(F45="","",IFERROR(INT(F45-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K45">
+        <f>IF(J45="","",IF(J45&lt;0,"Expired",IF(J45&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L45" t="n">
         <v>1</v>
@@ -3216,13 +3230,13 @@
       <c r="I46" t="n">
         <v>3391</v>
       </c>
-      <c r="J46" t="n">
-        <v>153</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J46">
+        <f>IF(F46="","",IFERROR(INT(F46-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K46">
+        <f>IF(J46="","",IF(J46&lt;0,"Expired",IF(J46&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L46" t="n">
         <v>1</v>
@@ -3277,13 +3291,13 @@
       <c r="I47" t="n">
         <v>3391</v>
       </c>
-      <c r="J47" t="n">
-        <v>153</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J47">
+        <f>IF(F47="","",IFERROR(INT(F47-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K47">
+        <f>IF(J47="","",IF(J47&lt;0,"Expired",IF(J47&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L47" t="n">
         <v>1</v>
@@ -3338,13 +3352,13 @@
       <c r="I48" t="n">
         <v>3391</v>
       </c>
-      <c r="J48" t="n">
-        <v>153</v>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J48">
+        <f>IF(F48="","",IFERROR(INT(F48-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K48">
+        <f>IF(J48="","",IF(J48&lt;0,"Expired",IF(J48&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L48" t="n">
         <v>1</v>
@@ -3399,13 +3413,13 @@
       <c r="I49" t="n">
         <v>3391</v>
       </c>
-      <c r="J49" t="n">
-        <v>153</v>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J49">
+        <f>IF(F49="","",IFERROR(INT(F49-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K49">
+        <f>IF(J49="","",IF(J49&lt;0,"Expired",IF(J49&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L49" t="n">
         <v>1</v>
@@ -3460,13 +3474,13 @@
       <c r="I50" t="n">
         <v>3331</v>
       </c>
-      <c r="J50" t="n">
-        <v>298</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J50">
+        <f>IF(F50="","",IFERROR(INT(F50-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K50">
+        <f>IF(J50="","",IF(J50&lt;0,"Expired",IF(J50&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L50" t="n">
         <v>1</v>
@@ -3521,13 +3535,13 @@
       <c r="I51" t="n">
         <v>3331</v>
       </c>
-      <c r="J51" t="n">
-        <v>298</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J51">
+        <f>IF(F51="","",IFERROR(INT(F51-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K51">
+        <f>IF(J51="","",IF(J51&lt;0,"Expired",IF(J51&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L51" t="n">
         <v>1</v>
@@ -3582,13 +3596,13 @@
       <c r="I52" t="n">
         <v>3331</v>
       </c>
-      <c r="J52" t="n">
-        <v>298</v>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J52">
+        <f>IF(F52="","",IFERROR(INT(F52-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K52">
+        <f>IF(J52="","",IF(J52&lt;0,"Expired",IF(J52&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L52" t="n">
         <v>1</v>
@@ -3643,13 +3657,13 @@
       <c r="I53" t="n">
         <v>3331</v>
       </c>
-      <c r="J53" t="n">
-        <v>298</v>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J53">
+        <f>IF(F53="","",IFERROR(INT(F53-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K53">
+        <f>IF(J53="","",IF(J53&lt;0,"Expired",IF(J53&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L53" t="n">
         <v>1</v>
@@ -3704,13 +3718,13 @@
       <c r="I54" t="n">
         <v>3331</v>
       </c>
-      <c r="J54" t="n">
-        <v>298</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J54">
+        <f>IF(F54="","",IFERROR(INT(F54-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K54">
+        <f>IF(J54="","",IF(J54&lt;0,"Expired",IF(J54&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L54" t="n">
         <v>1</v>
@@ -3765,13 +3779,13 @@
       <c r="I55" t="n">
         <v>3331</v>
       </c>
-      <c r="J55" t="n">
-        <v>298</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J55">
+        <f>IF(F55="","",IFERROR(INT(F55-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K55">
+        <f>IF(J55="","",IF(J55&lt;0,"Expired",IF(J55&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L55" t="n">
         <v>1</v>
@@ -3826,13 +3840,13 @@
       <c r="I56" t="n">
         <v>3331</v>
       </c>
-      <c r="J56" t="n">
-        <v>298</v>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J56">
+        <f>IF(F56="","",IFERROR(INT(F56-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K56">
+        <f>IF(J56="","",IF(J56&lt;0,"Expired",IF(J56&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -3887,13 +3901,13 @@
       <c r="I57" t="n">
         <v>6590</v>
       </c>
-      <c r="J57" t="n">
-        <v>337</v>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J57">
+        <f>IF(F57="","",IFERROR(INT(F57-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K57">
+        <f>IF(J57="","",IF(J57&lt;0,"Expired",IF(J57&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L57" t="n">
         <v>1</v>
@@ -3948,13 +3962,13 @@
       <c r="I58" t="n">
         <v>6590</v>
       </c>
-      <c r="J58" t="n">
-        <v>347</v>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J58">
+        <f>IF(F58="","",IFERROR(INT(F58-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K58">
+        <f>IF(J58="","",IF(J58&lt;0,"Expired",IF(J58&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L58" t="n">
         <v>1</v>
@@ -4009,13 +4023,13 @@
       <c r="I59" t="n">
         <v>7151</v>
       </c>
-      <c r="J59" t="n">
-        <v>295</v>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J59">
+        <f>IF(F59="","",IFERROR(INT(F59-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K59">
+        <f>IF(J59="","",IF(J59&lt;0,"Expired",IF(J59&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L59" t="n">
         <v>1</v>
@@ -4070,13 +4084,13 @@
       <c r="I60" t="n">
         <v>7151</v>
       </c>
-      <c r="J60" t="n">
-        <v>295</v>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J60">
+        <f>IF(F60="","",IFERROR(INT(F60-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K60">
+        <f>IF(J60="","",IF(J60&lt;0,"Expired",IF(J60&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L60" t="n">
         <v>1</v>
@@ -4131,13 +4145,13 @@
       <c r="I61" t="n">
         <v>7101</v>
       </c>
-      <c r="J61" t="n">
-        <v>269</v>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J61">
+        <f>IF(F61="","",IFERROR(INT(F61-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K61">
+        <f>IF(J61="","",IF(J61&lt;0,"Expired",IF(J61&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L61" t="n">
         <v>1</v>
@@ -4192,13 +4206,13 @@
       <c r="I62" t="n">
         <v>7101</v>
       </c>
-      <c r="J62" t="n">
-        <v>269</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J62">
+        <f>IF(F62="","",IFERROR(INT(F62-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K62">
+        <f>IF(J62="","",IF(J62&lt;0,"Expired",IF(J62&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L62" t="n">
         <v>1</v>
@@ -4253,13 +4267,13 @@
       <c r="I63" t="n">
         <v>6711</v>
       </c>
-      <c r="J63" t="n">
-        <v>311</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J63">
+        <f>IF(F63="","",IFERROR(INT(F63-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K63">
+        <f>IF(J63="","",IF(J63&lt;0,"Expired",IF(J63&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L63" t="n">
         <v>1</v>
@@ -4314,13 +4328,13 @@
       <c r="I64" t="n">
         <v>6950</v>
       </c>
-      <c r="J64" t="n">
-        <v>283</v>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J64">
+        <f>IF(F64="","",IFERROR(INT(F64-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K64">
+        <f>IF(J64="","",IF(J64&lt;0,"Expired",IF(J64&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L64" t="n">
         <v>1</v>
@@ -4375,13 +4389,13 @@
       <c r="I65" t="n">
         <v>6950</v>
       </c>
-      <c r="J65" t="n">
-        <v>283</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J65">
+        <f>IF(F65="","",IFERROR(INT(F65-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K65">
+        <f>IF(J65="","",IF(J65&lt;0,"Expired",IF(J65&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L65" t="n">
         <v>1</v>
@@ -4436,13 +4450,13 @@
       <c r="I66" t="n">
         <v>7151</v>
       </c>
-      <c r="J66" t="n">
-        <v>301</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J66">
+        <f>IF(F66="","",IFERROR(INT(F66-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K66">
+        <f>IF(J66="","",IF(J66&lt;0,"Expired",IF(J66&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L66" t="n">
         <v>1</v>
@@ -4497,13 +4511,13 @@
       <c r="I67" t="n">
         <v>6972</v>
       </c>
-      <c r="J67" t="n">
-        <v>202</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J67">
+        <f>IF(F67="","",IFERROR(INT(F67-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K67">
+        <f>IF(J67="","",IF(J67&lt;0,"Expired",IF(J67&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L67" t="n">
         <v>1</v>
@@ -4558,13 +4572,13 @@
       <c r="I68" t="n">
         <v>6913</v>
       </c>
-      <c r="J68" t="n">
-        <v>267</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J68">
+        <f>IF(F68="","",IFERROR(INT(F68-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K68">
+        <f>IF(J68="","",IF(J68&lt;0,"Expired",IF(J68&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L68" t="n">
         <v>1</v>
@@ -4619,13 +4633,13 @@
       <c r="I69" t="n">
         <v>7101</v>
       </c>
-      <c r="J69" t="n">
-        <v>273</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J69">
+        <f>IF(F69="","",IFERROR(INT(F69-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K69">
+        <f>IF(J69="","",IF(J69&lt;0,"Expired",IF(J69&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L69" t="n">
         <v>1</v>
@@ -4680,13 +4694,13 @@
       <c r="I70" t="n">
         <v>7101</v>
       </c>
-      <c r="J70" t="n">
-        <v>273</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J70">
+        <f>IF(F70="","",IFERROR(INT(F70-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K70">
+        <f>IF(J70="","",IF(J70&lt;0,"Expired",IF(J70&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L70" t="n">
         <v>1</v>
@@ -4741,13 +4755,13 @@
       <c r="I71" t="n">
         <v>7101</v>
       </c>
-      <c r="J71" t="n">
-        <v>269</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J71">
+        <f>IF(F71="","",IFERROR(INT(F71-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K71">
+        <f>IF(J71="","",IF(J71&lt;0,"Expired",IF(J71&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L71" t="n">
         <v>1</v>
@@ -4802,13 +4816,13 @@
       <c r="I72" t="n">
         <v>7017</v>
       </c>
-      <c r="J72" t="n">
-        <v>267</v>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J72">
+        <f>IF(F72="","",IFERROR(INT(F72-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K72">
+        <f>IF(J72="","",IF(J72&lt;0,"Expired",IF(J72&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L72" t="n">
         <v>1</v>
@@ -4863,13 +4877,13 @@
       <c r="I73" t="n">
         <v>6950</v>
       </c>
-      <c r="J73" t="n">
-        <v>283</v>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J73">
+        <f>IF(F73="","",IFERROR(INT(F73-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K73">
+        <f>IF(J73="","",IF(J73&lt;0,"Expired",IF(J73&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -4924,13 +4938,13 @@
       <c r="I74" t="n">
         <v>7101</v>
       </c>
-      <c r="J74" t="n">
-        <v>271</v>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J74">
+        <f>IF(F74="","",IFERROR(INT(F74-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K74">
+        <f>IF(J74="","",IF(J74&lt;0,"Expired",IF(J74&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L74" t="n">
         <v>1</v>
@@ -4985,13 +4999,13 @@
       <c r="I75" t="n">
         <v>7101</v>
       </c>
-      <c r="J75" t="n">
-        <v>271</v>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J75">
+        <f>IF(F75="","",IFERROR(INT(F75-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K75">
+        <f>IF(J75="","",IF(J75&lt;0,"Expired",IF(J75&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L75" t="n">
         <v>1</v>
@@ -5046,13 +5060,13 @@
       <c r="I76" t="n">
         <v>6950</v>
       </c>
-      <c r="J76" t="n">
-        <v>287</v>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J76">
+        <f>IF(F76="","",IFERROR(INT(F76-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K76">
+        <f>IF(J76="","",IF(J76&lt;0,"Expired",IF(J76&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L76" t="n">
         <v>1</v>
@@ -5107,13 +5121,13 @@
       <c r="I77" t="n">
         <v>6950</v>
       </c>
-      <c r="J77" t="n">
-        <v>287</v>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J77">
+        <f>IF(F77="","",IFERROR(INT(F77-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K77">
+        <f>IF(J77="","",IF(J77&lt;0,"Expired",IF(J77&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L77" t="n">
         <v>1</v>
@@ -5168,13 +5182,13 @@
       <c r="I78" t="n">
         <v>6950</v>
       </c>
-      <c r="J78" t="n">
-        <v>287</v>
-      </c>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J78">
+        <f>IF(F78="","",IFERROR(INT(F78-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K78">
+        <f>IF(J78="","",IF(J78&lt;0,"Expired",IF(J78&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L78" t="n">
         <v>1</v>
@@ -5229,13 +5243,13 @@
       <c r="I79" t="n">
         <v>7101</v>
       </c>
-      <c r="J79" t="n">
-        <v>271</v>
-      </c>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J79">
+        <f>IF(F79="","",IFERROR(INT(F79-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K79">
+        <f>IF(J79="","",IF(J79&lt;0,"Expired",IF(J79&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L79" t="n">
         <v>1</v>
@@ -5286,13 +5300,13 @@
       <c r="I80" t="n">
         <v>7101.24</v>
       </c>
-      <c r="J80" t="n">
-        <v>273</v>
-      </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J80">
+        <f>IF(F80="","",IFERROR(INT(F80-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K80">
+        <f>IF(J80="","",IF(J80&lt;0,"Expired",IF(J80&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L80" t="n">
         <v>1</v>
@@ -5347,13 +5361,13 @@
       <c r="I81" t="n">
         <v>7101</v>
       </c>
-      <c r="J81" t="n">
-        <v>272</v>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J81">
+        <f>IF(F81="","",IFERROR(INT(F81-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K81">
+        <f>IF(J81="","",IF(J81&lt;0,"Expired",IF(J81&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L81" t="n">
         <v>1</v>
@@ -5408,13 +5422,13 @@
       <c r="I82" t="n">
         <v>7101</v>
       </c>
-      <c r="J82" t="n">
-        <v>272</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J82">
+        <f>IF(F82="","",IFERROR(INT(F82-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K82">
+        <f>IF(J82="","",IF(J82&lt;0,"Expired",IF(J82&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L82" t="n">
         <v>1</v>
@@ -5469,13 +5483,13 @@
       <c r="I83" t="n">
         <v>7353.76</v>
       </c>
-      <c r="J83" t="n">
-        <v>299</v>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J83">
+        <f>IF(F83="","",IFERROR(INT(F83-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K83">
+        <f>IF(J83="","",IF(J83&lt;0,"Expired",IF(J83&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L83" t="n">
         <v>1</v>
@@ -5530,13 +5544,13 @@
       <c r="I84" t="n">
         <v>7101</v>
       </c>
-      <c r="J84" t="n">
-        <v>273</v>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J84">
+        <f>IF(F84="","",IFERROR(INT(F84-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K84">
+        <f>IF(J84="","",IF(J84&lt;0,"Expired",IF(J84&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L84" t="n">
         <v>1</v>
@@ -5591,13 +5605,13 @@
       <c r="I85" t="n">
         <v>7017</v>
       </c>
-      <c r="J85" t="n">
-        <v>278</v>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J85">
+        <f>IF(F85="","",IFERROR(INT(F85-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K85">
+        <f>IF(J85="","",IF(J85&lt;0,"Expired",IF(J85&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L85" t="n">
         <v>1</v>
@@ -5652,13 +5666,13 @@
       <c r="I86" t="n">
         <v>7017</v>
       </c>
-      <c r="J86" t="n">
-        <v>278</v>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J86">
+        <f>IF(F86="","",IFERROR(INT(F86-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K86">
+        <f>IF(J86="","",IF(J86&lt;0,"Expired",IF(J86&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L86" t="n">
         <v>1</v>
@@ -5713,13 +5727,13 @@
       <c r="I87" t="n">
         <v>7017</v>
       </c>
-      <c r="J87" t="n">
-        <v>279</v>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J87">
+        <f>IF(F87="","",IFERROR(INT(F87-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K87">
+        <f>IF(J87="","",IF(J87&lt;0,"Expired",IF(J87&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L87" t="n">
         <v>1</v>
@@ -5774,13 +5788,13 @@
       <c r="I88" t="n">
         <v>7101</v>
       </c>
-      <c r="J88" t="n">
-        <v>276</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J88">
+        <f>IF(F88="","",IFERROR(INT(F88-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K88">
+        <f>IF(J88="","",IF(J88&lt;0,"Expired",IF(J88&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L88" t="n">
         <v>1</v>
@@ -5835,13 +5849,13 @@
       <c r="I89" t="n">
         <v>7151</v>
       </c>
-      <c r="J89" t="n">
-        <v>293</v>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J89">
+        <f>IF(F89="","",IFERROR(INT(F89-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K89">
+        <f>IF(J89="","",IF(J89&lt;0,"Expired",IF(J89&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L89" t="n">
         <v>1</v>
@@ -5896,13 +5910,13 @@
       <c r="I90" t="n">
         <v>6962</v>
       </c>
-      <c r="J90" t="n">
-        <v>304</v>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J90">
+        <f>IF(F90="","",IFERROR(INT(F90-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K90">
+        <f>IF(J90="","",IF(J90&lt;0,"Expired",IF(J90&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L90" t="n">
         <v>1</v>
@@ -5957,13 +5971,13 @@
       <c r="I91" t="n">
         <v>6757.86</v>
       </c>
-      <c r="J91" t="n">
-        <v>321</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J91">
+        <f>IF(F91="","",IFERROR(INT(F91-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K91">
+        <f>IF(J91="","",IF(J91&lt;0,"Expired",IF(J91&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L91" t="n">
         <v>1</v>
@@ -6018,13 +6032,13 @@
       <c r="I92" t="n">
         <v>7150.8</v>
       </c>
-      <c r="J92" t="n">
-        <v>283</v>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J92">
+        <f>IF(F92="","",IFERROR(INT(F92-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K92">
+        <f>IF(J92="","",IF(J92&lt;0,"Expired",IF(J92&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L92" t="n">
         <v>1</v>
@@ -6079,13 +6093,13 @@
       <c r="I93" t="n">
         <v>7151</v>
       </c>
-      <c r="J93" t="n">
-        <v>301</v>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J93">
+        <f>IF(F93="","",IFERROR(INT(F93-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K93">
+        <f>IF(J93="","",IF(J93&lt;0,"Expired",IF(J93&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L93" t="n">
         <v>1</v>
@@ -6140,13 +6154,13 @@
       <c r="I94" t="n">
         <v>7304</v>
       </c>
-      <c r="J94" t="n">
-        <v>295</v>
-      </c>
-      <c r="K94" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J94">
+        <f>IF(F94="","",IFERROR(INT(F94-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K94">
+        <f>IF(J94="","",IF(J94&lt;0,"Expired",IF(J94&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L94" t="n">
         <v>1</v>
@@ -6201,13 +6215,13 @@
       <c r="I95" t="n">
         <v>6962</v>
       </c>
-      <c r="J95" t="n">
-        <v>312</v>
-      </c>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J95">
+        <f>IF(F95="","",IFERROR(INT(F95-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K95">
+        <f>IF(J95="","",IF(J95&lt;0,"Expired",IF(J95&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L95" t="n">
         <v>1</v>
@@ -6262,13 +6276,13 @@
       <c r="I96" t="n">
         <v>7151</v>
       </c>
-      <c r="J96" t="n">
-        <v>302</v>
-      </c>
-      <c r="K96" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J96">
+        <f>IF(F96="","",IFERROR(INT(F96-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K96">
+        <f>IF(J96="","",IF(J96&lt;0,"Expired",IF(J96&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L96" t="n">
         <v>1</v>
@@ -6323,13 +6337,13 @@
       <c r="I97" t="n">
         <v>7151</v>
       </c>
-      <c r="J97" t="n">
-        <v>302</v>
-      </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J97">
+        <f>IF(F97="","",IFERROR(INT(F97-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K97">
+        <f>IF(J97="","",IF(J97&lt;0,"Expired",IF(J97&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L97" t="n">
         <v>1</v>
@@ -6384,13 +6398,13 @@
       <c r="I98" t="n">
         <v>6711</v>
       </c>
-      <c r="J98" t="n">
-        <v>313</v>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J98">
+        <f>IF(F98="","",IFERROR(INT(F98-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K98">
+        <f>IF(J98="","",IF(J98&lt;0,"Expired",IF(J98&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L98" t="n">
         <v>1</v>
@@ -6445,13 +6459,13 @@
       <c r="I99" t="n">
         <v>6757.86</v>
       </c>
-      <c r="J99" t="n">
-        <v>308</v>
-      </c>
-      <c r="K99" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J99">
+        <f>IF(F99="","",IFERROR(INT(F99-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K99">
+        <f>IF(J99="","",IF(J99&lt;0,"Expired",IF(J99&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L99" t="n">
         <v>1</v>
@@ -6506,13 +6520,13 @@
       <c r="I100" t="n">
         <v>6757.86</v>
       </c>
-      <c r="J100" t="n">
-        <v>308</v>
-      </c>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J100">
+        <f>IF(F100="","",IFERROR(INT(F100-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K100">
+        <f>IF(J100="","",IF(J100&lt;0,"Expired",IF(J100&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L100" t="n">
         <v>1</v>
@@ -6567,13 +6581,13 @@
       <c r="I101" t="n">
         <v>6757.86</v>
       </c>
-      <c r="J101" t="n">
-        <v>308</v>
-      </c>
-      <c r="K101" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J101">
+        <f>IF(F101="","",IFERROR(INT(F101-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K101">
+        <f>IF(J101="","",IF(J101&lt;0,"Expired",IF(J101&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L101" t="n">
         <v>1</v>
@@ -6628,13 +6642,13 @@
       <c r="I102" t="n">
         <v>6757.86</v>
       </c>
-      <c r="J102" t="n">
-        <v>311</v>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J102">
+        <f>IF(F102="","",IFERROR(INT(F102-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K102">
+        <f>IF(J102="","",IF(J102&lt;0,"Expired",IF(J102&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L102" t="n">
         <v>1</v>
@@ -6689,13 +6703,13 @@
       <c r="I103" t="n">
         <v>6266</v>
       </c>
-      <c r="J103" t="n">
-        <v>337</v>
-      </c>
-      <c r="K103" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J103">
+        <f>IF(F103="","",IFERROR(INT(F103-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K103">
+        <f>IF(J103="","",IF(J103&lt;0,"Expired",IF(J103&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L103" t="n">
         <v>1</v>
@@ -6750,13 +6764,13 @@
       <c r="I104" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J104" t="n">
-        <v>342</v>
-      </c>
-      <c r="K104" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J104">
+        <f>IF(F104="","",IFERROR(INT(F104-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K104">
+        <f>IF(J104="","",IF(J104&lt;0,"Expired",IF(J104&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L104" t="n">
         <v>1</v>
@@ -6811,13 +6825,13 @@
       <c r="I105" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J105" t="n">
-        <v>342</v>
-      </c>
-      <c r="K105" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J105">
+        <f>IF(F105="","",IFERROR(INT(F105-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K105">
+        <f>IF(J105="","",IF(J105&lt;0,"Expired",IF(J105&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L105" t="n">
         <v>1</v>
@@ -6872,13 +6886,13 @@
       <c r="I106" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J106" t="n">
-        <v>342</v>
-      </c>
-      <c r="K106" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J106">
+        <f>IF(F106="","",IFERROR(INT(F106-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K106">
+        <f>IF(J106="","",IF(J106&lt;0,"Expired",IF(J106&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L106" t="n">
         <v>1</v>
@@ -6933,13 +6947,13 @@
       <c r="I107" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J107" t="n">
-        <v>342</v>
-      </c>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J107">
+        <f>IF(F107="","",IFERROR(INT(F107-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K107">
+        <f>IF(J107="","",IF(J107&lt;0,"Expired",IF(J107&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L107" t="n">
         <v>1</v>
@@ -6994,13 +7008,13 @@
       <c r="I108" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J108" t="n">
-        <v>342</v>
-      </c>
-      <c r="K108" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J108">
+        <f>IF(F108="","",IFERROR(INT(F108-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K108">
+        <f>IF(J108="","",IF(J108&lt;0,"Expired",IF(J108&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L108" t="n">
         <v>1</v>
@@ -7055,13 +7069,13 @@
       <c r="I109" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J109" t="n">
-        <v>342</v>
-      </c>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J109">
+        <f>IF(F109="","",IFERROR(INT(F109-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K109">
+        <f>IF(J109="","",IF(J109&lt;0,"Expired",IF(J109&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L109" t="n">
         <v>1</v>
@@ -7116,13 +7130,13 @@
       <c r="I110" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J110" t="n">
-        <v>342</v>
-      </c>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J110">
+        <f>IF(F110="","",IFERROR(INT(F110-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K110">
+        <f>IF(J110="","",IF(J110&lt;0,"Expired",IF(J110&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L110" t="n">
         <v>1</v>
@@ -7177,13 +7191,13 @@
       <c r="I111" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J111" t="n">
-        <v>342</v>
-      </c>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J111">
+        <f>IF(F111="","",IFERROR(INT(F111-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K111">
+        <f>IF(J111="","",IF(J111&lt;0,"Expired",IF(J111&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L111" t="n">
         <v>1</v>
@@ -7238,13 +7252,13 @@
       <c r="I112" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J112" t="n">
-        <v>342</v>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J112">
+        <f>IF(F112="","",IFERROR(INT(F112-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K112">
+        <f>IF(J112="","",IF(J112&lt;0,"Expired",IF(J112&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L112" t="n">
         <v>1</v>
@@ -7299,13 +7313,13 @@
       <c r="I113" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J113" t="n">
-        <v>342</v>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J113">
+        <f>IF(F113="","",IFERROR(INT(F113-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K113">
+        <f>IF(J113="","",IF(J113&lt;0,"Expired",IF(J113&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L113" t="n">
         <v>1</v>
@@ -7360,13 +7374,13 @@
       <c r="I114" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J114" t="n">
-        <v>342</v>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J114">
+        <f>IF(F114="","",IFERROR(INT(F114-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K114">
+        <f>IF(J114="","",IF(J114&lt;0,"Expired",IF(J114&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L114" t="n">
         <v>1</v>
@@ -7421,13 +7435,13 @@
       <c r="I115" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J115" t="n">
-        <v>342</v>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J115">
+        <f>IF(F115="","",IFERROR(INT(F115-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K115">
+        <f>IF(J115="","",IF(J115&lt;0,"Expired",IF(J115&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L115" t="n">
         <v>1</v>
@@ -7482,13 +7496,13 @@
       <c r="I116" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J116" t="n">
-        <v>342</v>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J116">
+        <f>IF(F116="","",IFERROR(INT(F116-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K116">
+        <f>IF(J116="","",IF(J116&lt;0,"Expired",IF(J116&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L116" t="n">
         <v>1</v>
@@ -7543,13 +7557,13 @@
       <c r="I117" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J117" t="n">
-        <v>342</v>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J117">
+        <f>IF(F117="","",IFERROR(INT(F117-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K117">
+        <f>IF(J117="","",IF(J117&lt;0,"Expired",IF(J117&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L117" t="n">
         <v>1</v>
@@ -7604,13 +7618,13 @@
       <c r="I118" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J118" t="n">
-        <v>342</v>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J118">
+        <f>IF(F118="","",IFERROR(INT(F118-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K118">
+        <f>IF(J118="","",IF(J118&lt;0,"Expired",IF(J118&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L118" t="n">
         <v>1</v>
@@ -7665,13 +7679,13 @@
       <c r="I119" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J119" t="n">
-        <v>342</v>
-      </c>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J119">
+        <f>IF(F119="","",IFERROR(INT(F119-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K119">
+        <f>IF(J119="","",IF(J119&lt;0,"Expired",IF(J119&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L119" t="n">
         <v>1</v>
@@ -7726,13 +7740,13 @@
       <c r="I120" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J120" t="n">
-        <v>342</v>
-      </c>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J120">
+        <f>IF(F120="","",IFERROR(INT(F120-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K120">
+        <f>IF(J120="","",IF(J120&lt;0,"Expired",IF(J120&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L120" t="n">
         <v>1</v>
@@ -7787,13 +7801,13 @@
       <c r="I121" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J121" t="n">
-        <v>342</v>
-      </c>
-      <c r="K121" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J121">
+        <f>IF(F121="","",IFERROR(INT(F121-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K121">
+        <f>IF(J121="","",IF(J121&lt;0,"Expired",IF(J121&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L121" t="n">
         <v>1</v>
@@ -7848,13 +7862,13 @@
       <c r="I122" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J122" t="n">
-        <v>342</v>
-      </c>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J122">
+        <f>IF(F122="","",IFERROR(INT(F122-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K122">
+        <f>IF(J122="","",IF(J122&lt;0,"Expired",IF(J122&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L122" t="n">
         <v>1</v>
@@ -7909,13 +7923,13 @@
       <c r="I123" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J123" t="n">
-        <v>342</v>
-      </c>
-      <c r="K123" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J123">
+        <f>IF(F123="","",IFERROR(INT(F123-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K123">
+        <f>IF(J123="","",IF(J123&lt;0,"Expired",IF(J123&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L123" t="n">
         <v>1</v>
@@ -7970,13 +7984,13 @@
       <c r="I124" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J124" t="n">
-        <v>342</v>
-      </c>
-      <c r="K124" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J124">
+        <f>IF(F124="","",IFERROR(INT(F124-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K124">
+        <f>IF(J124="","",IF(J124&lt;0,"Expired",IF(J124&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L124" t="n">
         <v>1</v>
@@ -8031,13 +8045,13 @@
       <c r="I125" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J125" t="n">
-        <v>342</v>
-      </c>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J125">
+        <f>IF(F125="","",IFERROR(INT(F125-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K125">
+        <f>IF(J125="","",IF(J125&lt;0,"Expired",IF(J125&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L125" t="n">
         <v>1</v>
@@ -8092,13 +8106,13 @@
       <c r="I126" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J126" t="n">
-        <v>342</v>
-      </c>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J126">
+        <f>IF(F126="","",IFERROR(INT(F126-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K126">
+        <f>IF(J126="","",IF(J126&lt;0,"Expired",IF(J126&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L126" t="n">
         <v>1</v>
@@ -8153,13 +8167,13 @@
       <c r="I127" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J127" t="n">
-        <v>342</v>
-      </c>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J127">
+        <f>IF(F127="","",IFERROR(INT(F127-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K127">
+        <f>IF(J127="","",IF(J127&lt;0,"Expired",IF(J127&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L127" t="n">
         <v>1</v>
@@ -8214,13 +8228,13 @@
       <c r="I128" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J128" t="n">
-        <v>342</v>
-      </c>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J128">
+        <f>IF(F128="","",IFERROR(INT(F128-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K128">
+        <f>IF(J128="","",IF(J128&lt;0,"Expired",IF(J128&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L128" t="n">
         <v>1</v>
@@ -8275,13 +8289,13 @@
       <c r="I129" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J129" t="n">
-        <v>342</v>
-      </c>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J129">
+        <f>IF(F129="","",IFERROR(INT(F129-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K129">
+        <f>IF(J129="","",IF(J129&lt;0,"Expired",IF(J129&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L129" t="n">
         <v>1</v>
@@ -8336,13 +8350,13 @@
       <c r="I130" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J130" t="n">
-        <v>342</v>
-      </c>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J130">
+        <f>IF(F130="","",IFERROR(INT(F130-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K130">
+        <f>IF(J130="","",IF(J130&lt;0,"Expired",IF(J130&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L130" t="n">
         <v>1</v>
@@ -8397,13 +8411,13 @@
       <c r="I131" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J131" t="n">
-        <v>342</v>
-      </c>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J131">
+        <f>IF(F131="","",IFERROR(INT(F131-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K131">
+        <f>IF(J131="","",IF(J131&lt;0,"Expired",IF(J131&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L131" t="n">
         <v>1</v>
@@ -8458,13 +8472,13 @@
       <c r="I132" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J132" t="n">
-        <v>342</v>
-      </c>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J132">
+        <f>IF(F132="","",IFERROR(INT(F132-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K132">
+        <f>IF(J132="","",IF(J132&lt;0,"Expired",IF(J132&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L132" t="n">
         <v>1</v>
@@ -8519,13 +8533,13 @@
       <c r="I133" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J133" t="n">
-        <v>342</v>
-      </c>
-      <c r="K133" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J133">
+        <f>IF(F133="","",IFERROR(INT(F133-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K133">
+        <f>IF(J133="","",IF(J133&lt;0,"Expired",IF(J133&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L133" t="n">
         <v>1</v>
@@ -8580,13 +8594,13 @@
       <c r="I134" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J134" t="n">
-        <v>342</v>
-      </c>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J134">
+        <f>IF(F134="","",IFERROR(INT(F134-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K134">
+        <f>IF(J134="","",IF(J134&lt;0,"Expired",IF(J134&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L134" t="n">
         <v>1</v>
@@ -8641,13 +8655,13 @@
       <c r="I135" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J135" t="n">
-        <v>342</v>
-      </c>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J135">
+        <f>IF(F135="","",IFERROR(INT(F135-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K135">
+        <f>IF(J135="","",IF(J135&lt;0,"Expired",IF(J135&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L135" t="n">
         <v>1</v>
@@ -8702,13 +8716,13 @@
       <c r="I136" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J136" t="n">
-        <v>342</v>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J136">
+        <f>IF(F136="","",IFERROR(INT(F136-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K136">
+        <f>IF(J136="","",IF(J136&lt;0,"Expired",IF(J136&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L136" t="n">
         <v>1</v>
@@ -8763,13 +8777,13 @@
       <c r="I137" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J137" t="n">
-        <v>342</v>
-      </c>
-      <c r="K137" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J137">
+        <f>IF(F137="","",IFERROR(INT(F137-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K137">
+        <f>IF(J137="","",IF(J137&lt;0,"Expired",IF(J137&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L137" t="n">
         <v>1</v>
@@ -8824,13 +8838,13 @@
       <c r="I138" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J138" t="n">
-        <v>342</v>
-      </c>
-      <c r="K138" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J138">
+        <f>IF(F138="","",IFERROR(INT(F138-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K138">
+        <f>IF(J138="","",IF(J138&lt;0,"Expired",IF(J138&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L138" t="n">
         <v>1</v>
@@ -8885,13 +8899,13 @@
       <c r="I139" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J139" t="n">
-        <v>342</v>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J139">
+        <f>IF(F139="","",IFERROR(INT(F139-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K139">
+        <f>IF(J139="","",IF(J139&lt;0,"Expired",IF(J139&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L139" t="n">
         <v>1</v>
@@ -8946,13 +8960,13 @@
       <c r="I140" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J140" t="n">
-        <v>342</v>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J140">
+        <f>IF(F140="","",IFERROR(INT(F140-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K140">
+        <f>IF(J140="","",IF(J140&lt;0,"Expired",IF(J140&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L140" t="n">
         <v>1</v>
@@ -9007,13 +9021,13 @@
       <c r="I141" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J141" t="n">
-        <v>342</v>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J141">
+        <f>IF(F141="","",IFERROR(INT(F141-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K141">
+        <f>IF(J141="","",IF(J141&lt;0,"Expired",IF(J141&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L141" t="n">
         <v>1</v>
@@ -9068,13 +9082,13 @@
       <c r="I142" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J142" t="n">
-        <v>342</v>
-      </c>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J142">
+        <f>IF(F142="","",IFERROR(INT(F142-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K142">
+        <f>IF(J142="","",IF(J142&lt;0,"Expired",IF(J142&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L142" t="n">
         <v>1</v>
@@ -9129,13 +9143,13 @@
       <c r="I143" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J143" t="n">
-        <v>342</v>
-      </c>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J143">
+        <f>IF(F143="","",IFERROR(INT(F143-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K143">
+        <f>IF(J143="","",IF(J143&lt;0,"Expired",IF(J143&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L143" t="n">
         <v>1</v>
@@ -9190,13 +9204,13 @@
       <c r="I144" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J144" t="n">
-        <v>342</v>
-      </c>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J144">
+        <f>IF(F144="","",IFERROR(INT(F144-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K144">
+        <f>IF(J144="","",IF(J144&lt;0,"Expired",IF(J144&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L144" t="n">
         <v>1</v>
@@ -9251,13 +9265,13 @@
       <c r="I145" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J145" t="n">
-        <v>342</v>
-      </c>
-      <c r="K145" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J145">
+        <f>IF(F145="","",IFERROR(INT(F145-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K145">
+        <f>IF(J145="","",IF(J145&lt;0,"Expired",IF(J145&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L145" t="n">
         <v>1</v>
@@ -9312,13 +9326,13 @@
       <c r="I146" t="n">
         <v>5654.85</v>
       </c>
-      <c r="J146" t="n">
-        <v>342</v>
-      </c>
-      <c r="K146" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J146">
+        <f>IF(F146="","",IFERROR(INT(F146-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K146">
+        <f>IF(J146="","",IF(J146&lt;0,"Expired",IF(J146&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L146" t="n">
         <v>1</v>
@@ -9373,13 +9387,13 @@
       <c r="I147" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J147" t="n">
-        <v>342</v>
-      </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J147">
+        <f>IF(F147="","",IFERROR(INT(F147-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K147">
+        <f>IF(J147="","",IF(J147&lt;0,"Expired",IF(J147&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L147" t="n">
         <v>1</v>
@@ -9434,13 +9448,13 @@
       <c r="I148" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J148" t="n">
-        <v>342</v>
-      </c>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J148">
+        <f>IF(F148="","",IFERROR(INT(F148-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K148">
+        <f>IF(J148="","",IF(J148&lt;0,"Expired",IF(J148&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L148" t="n">
         <v>1</v>
@@ -9495,13 +9509,13 @@
       <c r="I149" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J149" t="n">
-        <v>342</v>
-      </c>
-      <c r="K149" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J149">
+        <f>IF(F149="","",IFERROR(INT(F149-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K149">
+        <f>IF(J149="","",IF(J149&lt;0,"Expired",IF(J149&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L149" t="n">
         <v>1</v>
@@ -9556,13 +9570,13 @@
       <c r="I150" t="n">
         <v>7954</v>
       </c>
-      <c r="J150" t="n">
-        <v>404</v>
-      </c>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J150">
+        <f>IF(F150="","",IFERROR(INT(F150-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K150">
+        <f>IF(J150="","",IF(J150&lt;0,"Expired",IF(J150&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L150" t="n">
         <v>1</v>
@@ -9617,13 +9631,13 @@
       <c r="I151" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J151" t="n">
-        <v>342</v>
-      </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J151">
+        <f>IF(F151="","",IFERROR(INT(F151-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K151">
+        <f>IF(J151="","",IF(J151&lt;0,"Expired",IF(J151&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L151" t="n">
         <v>1</v>
@@ -9678,13 +9692,13 @@
       <c r="I152" t="n">
         <v>5906</v>
       </c>
-      <c r="J152" t="n">
-        <v>342</v>
-      </c>
-      <c r="K152" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J152">
+        <f>IF(F152="","",IFERROR(INT(F152-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K152">
+        <f>IF(J152="","",IF(J152&lt;0,"Expired",IF(J152&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L152" t="n">
         <v>1</v>
@@ -9739,13 +9753,13 @@
       <c r="I153" t="n">
         <v>5922.63</v>
       </c>
-      <c r="J153" t="n">
-        <v>342</v>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J153">
+        <f>IF(F153="","",IFERROR(INT(F153-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K153">
+        <f>IF(J153="","",IF(J153&lt;0,"Expired",IF(J153&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L153" t="n">
         <v>1</v>
@@ -9800,13 +9814,13 @@
       <c r="I154" t="n">
         <v>6451</v>
       </c>
-      <c r="J154" t="n">
-        <v>319</v>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J154">
+        <f>IF(F154="","",IFERROR(INT(F154-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K154">
+        <f>IF(J154="","",IF(J154&lt;0,"Expired",IF(J154&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L154" t="n">
         <v>1</v>
@@ -9861,13 +9875,13 @@
       <c r="I155" t="n">
         <v>6451</v>
       </c>
-      <c r="J155" t="n">
-        <v>319</v>
-      </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J155">
+        <f>IF(F155="","",IFERROR(INT(F155-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K155">
+        <f>IF(J155="","",IF(J155&lt;0,"Expired",IF(J155&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L155" t="n">
         <v>1</v>
@@ -9922,13 +9936,13 @@
       <c r="I156" t="n">
         <v>6451</v>
       </c>
-      <c r="J156" t="n">
-        <v>321</v>
-      </c>
-      <c r="K156" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J156">
+        <f>IF(F156="","",IFERROR(INT(F156-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K156">
+        <f>IF(J156="","",IF(J156&lt;0,"Expired",IF(J156&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L156" t="n">
         <v>1</v>
@@ -9983,13 +9997,13 @@
       <c r="I157" t="n">
         <v>7435</v>
       </c>
-      <c r="J157" t="n">
-        <v>320</v>
-      </c>
-      <c r="K157" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J157">
+        <f>IF(F157="","",IFERROR(INT(F157-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K157">
+        <f>IF(J157="","",IF(J157&lt;0,"Expired",IF(J157&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L157" t="n">
         <v>1</v>
@@ -10044,13 +10058,13 @@
       <c r="I158" t="n">
         <v>6998</v>
       </c>
-      <c r="J158" t="n">
-        <v>136</v>
-      </c>
-      <c r="K158" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J158">
+        <f>IF(F158="","",IFERROR(INT(F158-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K158">
+        <f>IF(J158="","",IF(J158&lt;0,"Expired",IF(J158&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L158" t="n">
         <v>1</v>
@@ -10105,13 +10119,13 @@
       <c r="I159" t="n">
         <v>6998</v>
       </c>
-      <c r="J159" t="n">
-        <v>136</v>
-      </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J159">
+        <f>IF(F159="","",IFERROR(INT(F159-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K159">
+        <f>IF(J159="","",IF(J159&lt;0,"Expired",IF(J159&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L159" t="n">
         <v>1</v>
@@ -10166,13 +10180,13 @@
       <c r="I160" t="n">
         <v>7439</v>
       </c>
-      <c r="J160" t="n">
-        <v>161</v>
-      </c>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J160">
+        <f>IF(F160="","",IFERROR(INT(F160-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K160">
+        <f>IF(J160="","",IF(J160&lt;0,"Expired",IF(J160&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L160" t="n">
         <v>1</v>
@@ -10227,13 +10241,13 @@
       <c r="I161" t="n">
         <v>2050</v>
       </c>
-      <c r="J161" t="n">
-        <v>269</v>
-      </c>
-      <c r="K161" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J161">
+        <f>IF(F161="","",IFERROR(INT(F161-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K161">
+        <f>IF(J161="","",IF(J161&lt;0,"Expired",IF(J161&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -10288,13 +10302,13 @@
       <c r="I162" t="n">
         <v>2050</v>
       </c>
-      <c r="J162" t="n">
-        <v>269</v>
-      </c>
-      <c r="K162" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J162">
+        <f>IF(F162="","",IFERROR(INT(F162-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K162">
+        <f>IF(J162="","",IF(J162&lt;0,"Expired",IF(J162&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L162" t="n">
         <v>1</v>
@@ -10349,13 +10363,13 @@
       <c r="I163" t="n">
         <v>2050</v>
       </c>
-      <c r="J163" t="n">
-        <v>269</v>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J163">
+        <f>IF(F163="","",IFERROR(INT(F163-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K163">
+        <f>IF(J163="","",IF(J163&lt;0,"Expired",IF(J163&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L163" t="n">
         <v>1</v>
@@ -10410,13 +10424,13 @@
       <c r="I164" t="n">
         <v>2050</v>
       </c>
-      <c r="J164" t="n">
-        <v>269</v>
-      </c>
-      <c r="K164" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J164">
+        <f>IF(F164="","",IFERROR(INT(F164-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K164">
+        <f>IF(J164="","",IF(J164&lt;0,"Expired",IF(J164&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L164" t="n">
         <v>1</v>
@@ -10471,13 +10485,13 @@
       <c r="I165" t="n">
         <v>2050</v>
       </c>
-      <c r="J165" t="n">
-        <v>269</v>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J165">
+        <f>IF(F165="","",IFERROR(INT(F165-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K165">
+        <f>IF(J165="","",IF(J165&lt;0,"Expired",IF(J165&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L165" t="n">
         <v>1</v>
@@ -10532,13 +10546,13 @@
       <c r="I166" t="n">
         <v>2050</v>
       </c>
-      <c r="J166" t="n">
-        <v>269</v>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J166">
+        <f>IF(F166="","",IFERROR(INT(F166-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K166">
+        <f>IF(J166="","",IF(J166&lt;0,"Expired",IF(J166&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L166" t="n">
         <v>1</v>
@@ -10593,13 +10607,13 @@
       <c r="I167" t="n">
         <v>2050</v>
       </c>
-      <c r="J167" t="n">
-        <v>269</v>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J167">
+        <f>IF(F167="","",IFERROR(INT(F167-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K167">
+        <f>IF(J167="","",IF(J167&lt;0,"Expired",IF(J167&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L167" t="n">
         <v>1</v>
@@ -10654,13 +10668,13 @@
       <c r="I168" t="n">
         <v>2050</v>
       </c>
-      <c r="J168" t="n">
-        <v>269</v>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J168">
+        <f>IF(F168="","",IFERROR(INT(F168-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K168">
+        <f>IF(J168="","",IF(J168&lt;0,"Expired",IF(J168&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L168" t="n">
         <v>1</v>
@@ -10715,13 +10729,13 @@
       <c r="I169" t="n">
         <v>5577</v>
       </c>
-      <c r="J169" t="n">
-        <v>46</v>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J169">
+        <f>IF(F169="","",IFERROR(INT(F169-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K169">
+        <f>IF(J169="","",IF(J169&lt;0,"Expired",IF(J169&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L169" t="n">
         <v>1</v>
@@ -10776,13 +10790,13 @@
       <c r="I170" t="n">
         <v>5577</v>
       </c>
-      <c r="J170" t="n">
-        <v>46</v>
-      </c>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J170">
+        <f>IF(F170="","",IFERROR(INT(F170-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K170">
+        <f>IF(J170="","",IF(J170&lt;0,"Expired",IF(J170&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L170" t="n">
         <v>1</v>
@@ -10837,13 +10851,13 @@
       <c r="I171" t="n">
         <v>5577</v>
       </c>
-      <c r="J171" t="n">
-        <v>46</v>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J171">
+        <f>IF(F171="","",IFERROR(INT(F171-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K171">
+        <f>IF(J171="","",IF(J171&lt;0,"Expired",IF(J171&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L171" t="n">
         <v>1</v>
@@ -10898,13 +10912,13 @@
       <c r="I172" t="n">
         <v>5577</v>
       </c>
-      <c r="J172" t="n">
-        <v>46</v>
-      </c>
-      <c r="K172" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J172">
+        <f>IF(F172="","",IFERROR(INT(F172-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K172">
+        <f>IF(J172="","",IF(J172&lt;0,"Expired",IF(J172&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L172" t="n">
         <v>1</v>
@@ -10959,13 +10973,13 @@
       <c r="I173" t="n">
         <v>7538</v>
       </c>
-      <c r="J173" t="n">
-        <v>79</v>
-      </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J173">
+        <f>IF(F173="","",IFERROR(INT(F173-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K173">
+        <f>IF(J173="","",IF(J173&lt;0,"Expired",IF(J173&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L173" t="n">
         <v>1</v>
@@ -11020,13 +11034,13 @@
       <c r="I174" t="n">
         <v>6990</v>
       </c>
-      <c r="J174" t="n">
-        <v>21</v>
-      </c>
-      <c r="K174" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J174">
+        <f>IF(F174="","",IFERROR(INT(F174-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K174">
+        <f>IF(J174="","",IF(J174&lt;0,"Expired",IF(J174&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L174" t="n">
         <v>1</v>
@@ -11081,13 +11095,13 @@
       <c r="I175" t="n">
         <v>7538</v>
       </c>
-      <c r="J175" t="n">
-        <v>79</v>
-      </c>
-      <c r="K175" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J175">
+        <f>IF(F175="","",IFERROR(INT(F175-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K175">
+        <f>IF(J175="","",IF(J175&lt;0,"Expired",IF(J175&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L175" t="n">
         <v>1</v>
@@ -11142,13 +11156,13 @@
       <c r="I176" t="n">
         <v>7538</v>
       </c>
-      <c r="J176" t="n">
-        <v>79</v>
-      </c>
-      <c r="K176" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J176">
+        <f>IF(F176="","",IFERROR(INT(F176-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K176">
+        <f>IF(J176="","",IF(J176&lt;0,"Expired",IF(J176&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L176" t="n">
         <v>1</v>
@@ -11203,13 +11217,13 @@
       <c r="I177" t="n">
         <v>7538</v>
       </c>
-      <c r="J177" t="n">
-        <v>79</v>
-      </c>
-      <c r="K177" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J177">
+        <f>IF(F177="","",IFERROR(INT(F177-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K177">
+        <f>IF(J177="","",IF(J177&lt;0,"Expired",IF(J177&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L177" t="n">
         <v>1</v>
@@ -11264,13 +11278,13 @@
       <c r="I178" t="n">
         <v>7538</v>
       </c>
-      <c r="J178" t="n">
-        <v>79</v>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J178">
+        <f>IF(F178="","",IFERROR(INT(F178-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K178">
+        <f>IF(J178="","",IF(J178&lt;0,"Expired",IF(J178&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L178" t="n">
         <v>1</v>
@@ -11325,13 +11339,13 @@
       <c r="I179" t="n">
         <v>7538</v>
       </c>
-      <c r="J179" t="n">
-        <v>79</v>
-      </c>
-      <c r="K179" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J179">
+        <f>IF(F179="","",IFERROR(INT(F179-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K179">
+        <f>IF(J179="","",IF(J179&lt;0,"Expired",IF(J179&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L179" t="n">
         <v>1</v>
@@ -11386,13 +11400,13 @@
       <c r="I180" t="n">
         <v>7538</v>
       </c>
-      <c r="J180" t="n">
-        <v>79</v>
-      </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J180">
+        <f>IF(F180="","",IFERROR(INT(F180-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K180">
+        <f>IF(J180="","",IF(J180&lt;0,"Expired",IF(J180&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L180" t="n">
         <v>1</v>
@@ -11447,13 +11461,13 @@
       <c r="I181" t="n">
         <v>7538</v>
       </c>
-      <c r="J181" t="n">
-        <v>79</v>
-      </c>
-      <c r="K181" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J181">
+        <f>IF(F181="","",IFERROR(INT(F181-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K181">
+        <f>IF(J181="","",IF(J181&lt;0,"Expired",IF(J181&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L181" t="n">
         <v>1</v>
@@ -11508,13 +11522,13 @@
       <c r="I182" t="n">
         <v>7538</v>
       </c>
-      <c r="J182" t="n">
-        <v>79</v>
-      </c>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J182">
+        <f>IF(F182="","",IFERROR(INT(F182-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K182">
+        <f>IF(J182="","",IF(J182&lt;0,"Expired",IF(J182&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L182" t="n">
         <v>1</v>
@@ -11569,13 +11583,13 @@
       <c r="I183" t="n">
         <v>7538</v>
       </c>
-      <c r="J183" t="n">
-        <v>79</v>
-      </c>
-      <c r="K183" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J183">
+        <f>IF(F183="","",IFERROR(INT(F183-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K183">
+        <f>IF(J183="","",IF(J183&lt;0,"Expired",IF(J183&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L183" t="n">
         <v>1</v>
@@ -11630,13 +11644,13 @@
       <c r="I184" t="n">
         <v>7538</v>
       </c>
-      <c r="J184" t="n">
-        <v>143</v>
-      </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J184">
+        <f>IF(F184="","",IFERROR(INT(F184-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K184">
+        <f>IF(J184="","",IF(J184&lt;0,"Expired",IF(J184&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L184" t="n">
         <v>1</v>
@@ -11691,13 +11705,13 @@
       <c r="I185" t="n">
         <v>7538</v>
       </c>
-      <c r="J185" t="n">
-        <v>143</v>
-      </c>
-      <c r="K185" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J185">
+        <f>IF(F185="","",IFERROR(INT(F185-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K185">
+        <f>IF(J185="","",IF(J185&lt;0,"Expired",IF(J185&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L185" t="n">
         <v>1</v>
@@ -11752,13 +11766,13 @@
       <c r="I186" t="n">
         <v>7538</v>
       </c>
-      <c r="J186" t="n">
-        <v>143</v>
-      </c>
-      <c r="K186" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J186">
+        <f>IF(F186="","",IFERROR(INT(F186-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K186">
+        <f>IF(J186="","",IF(J186&lt;0,"Expired",IF(J186&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L186" t="n">
         <v>1</v>
@@ -11813,13 +11827,13 @@
       <c r="I187" t="n">
         <v>7538</v>
       </c>
-      <c r="J187" t="n">
-        <v>143</v>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J187">
+        <f>IF(F187="","",IFERROR(INT(F187-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K187">
+        <f>IF(J187="","",IF(J187&lt;0,"Expired",IF(J187&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L187" t="n">
         <v>1</v>
@@ -11874,13 +11888,13 @@
       <c r="I188" t="n">
         <v>7538</v>
       </c>
-      <c r="J188" t="n">
-        <v>143</v>
-      </c>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J188">
+        <f>IF(F188="","",IFERROR(INT(F188-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K188">
+        <f>IF(J188="","",IF(J188&lt;0,"Expired",IF(J188&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L188" t="n">
         <v>1</v>
@@ -11935,13 +11949,13 @@
       <c r="I189" t="n">
         <v>7538</v>
       </c>
-      <c r="J189" t="n">
-        <v>143</v>
-      </c>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J189">
+        <f>IF(F189="","",IFERROR(INT(F189-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K189">
+        <f>IF(J189="","",IF(J189&lt;0,"Expired",IF(J189&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L189" t="n">
         <v>1</v>
@@ -11996,13 +12010,13 @@
       <c r="I190" t="n">
         <v>4085</v>
       </c>
-      <c r="J190" t="n">
-        <v>116</v>
-      </c>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J190">
+        <f>IF(F190="","",IFERROR(INT(F190-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K190">
+        <f>IF(J190="","",IF(J190&lt;0,"Expired",IF(J190&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L190" t="n">
         <v>1</v>
@@ -12057,13 +12071,13 @@
       <c r="I191" t="n">
         <v>4289</v>
       </c>
-      <c r="J191" t="n">
-        <v>143</v>
-      </c>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J191">
+        <f>IF(F191="","",IFERROR(INT(F191-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K191">
+        <f>IF(J191="","",IF(J191&lt;0,"Expired",IF(J191&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L191" t="n">
         <v>1</v>
@@ -12118,13 +12132,13 @@
       <c r="I192" t="n">
         <v>4289</v>
       </c>
-      <c r="J192" t="n">
-        <v>150</v>
-      </c>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J192">
+        <f>IF(F192="","",IFERROR(INT(F192-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K192">
+        <f>IF(J192="","",IF(J192&lt;0,"Expired",IF(J192&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L192" t="n">
         <v>1</v>
@@ -12179,13 +12193,13 @@
       <c r="I193" t="n">
         <v>4289</v>
       </c>
-      <c r="J193" t="n">
-        <v>150</v>
-      </c>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J193">
+        <f>IF(F193="","",IFERROR(INT(F193-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K193">
+        <f>IF(J193="","",IF(J193&lt;0,"Expired",IF(J193&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L193" t="n">
         <v>1</v>
@@ -12240,13 +12254,13 @@
       <c r="I194" t="n">
         <v>4289</v>
       </c>
-      <c r="J194" t="n">
-        <v>150</v>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J194">
+        <f>IF(F194="","",IFERROR(INT(F194-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K194">
+        <f>IF(J194="","",IF(J194&lt;0,"Expired",IF(J194&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L194" t="n">
         <v>1</v>
@@ -12301,13 +12315,13 @@
       <c r="I195" t="n">
         <v>4289</v>
       </c>
-      <c r="J195" t="n">
-        <v>150</v>
-      </c>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J195">
+        <f>IF(F195="","",IFERROR(INT(F195-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K195">
+        <f>IF(J195="","",IF(J195&lt;0,"Expired",IF(J195&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L195" t="n">
         <v>1</v>
@@ -12362,13 +12376,13 @@
       <c r="I196" t="n">
         <v>4289</v>
       </c>
-      <c r="J196" t="n">
-        <v>150</v>
-      </c>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J196">
+        <f>IF(F196="","",IFERROR(INT(F196-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K196">
+        <f>IF(J196="","",IF(J196&lt;0,"Expired",IF(J196&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L196" t="n">
         <v>1</v>
@@ -12423,13 +12437,13 @@
       <c r="I197" t="n">
         <v>4289</v>
       </c>
-      <c r="J197" t="n">
-        <v>150</v>
-      </c>
-      <c r="K197" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J197">
+        <f>IF(F197="","",IFERROR(INT(F197-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K197">
+        <f>IF(J197="","",IF(J197&lt;0,"Expired",IF(J197&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L197" t="n">
         <v>1</v>
@@ -12484,13 +12498,13 @@
       <c r="I198" t="n">
         <v>4289</v>
       </c>
-      <c r="J198" t="n">
-        <v>150</v>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J198">
+        <f>IF(F198="","",IFERROR(INT(F198-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K198">
+        <f>IF(J198="","",IF(J198&lt;0,"Expired",IF(J198&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L198" t="n">
         <v>1</v>
@@ -12545,13 +12559,13 @@
       <c r="I199" t="n">
         <v>4289</v>
       </c>
-      <c r="J199" t="n">
-        <v>150</v>
-      </c>
-      <c r="K199" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J199">
+        <f>IF(F199="","",IFERROR(INT(F199-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K199">
+        <f>IF(J199="","",IF(J199&lt;0,"Expired",IF(J199&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L199" t="n">
         <v>1</v>
@@ -12606,13 +12620,13 @@
       <c r="I200" t="n">
         <v>4289</v>
       </c>
-      <c r="J200" t="n">
-        <v>150</v>
-      </c>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J200">
+        <f>IF(F200="","",IFERROR(INT(F200-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K200">
+        <f>IF(J200="","",IF(J200&lt;0,"Expired",IF(J200&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L200" t="n">
         <v>1</v>
@@ -12667,13 +12681,13 @@
       <c r="I201" t="n">
         <v>4289</v>
       </c>
-      <c r="J201" t="n">
-        <v>150</v>
-      </c>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J201">
+        <f>IF(F201="","",IFERROR(INT(F201-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K201">
+        <f>IF(J201="","",IF(J201&lt;0,"Expired",IF(J201&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L201" t="n">
         <v>1</v>
@@ -12728,13 +12742,13 @@
       <c r="I202" t="n">
         <v>4289</v>
       </c>
-      <c r="J202" t="n">
-        <v>150</v>
-      </c>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J202">
+        <f>IF(F202="","",IFERROR(INT(F202-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K202">
+        <f>IF(J202="","",IF(J202&lt;0,"Expired",IF(J202&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L202" t="n">
         <v>1</v>
@@ -12789,13 +12803,13 @@
       <c r="I203" t="n">
         <v>4289</v>
       </c>
-      <c r="J203" t="n">
-        <v>150</v>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J203">
+        <f>IF(F203="","",IFERROR(INT(F203-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K203">
+        <f>IF(J203="","",IF(J203&lt;0,"Expired",IF(J203&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L203" t="n">
         <v>1</v>
@@ -12850,13 +12864,13 @@
       <c r="I204" t="n">
         <v>4289</v>
       </c>
-      <c r="J204" t="n">
-        <v>150</v>
-      </c>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J204">
+        <f>IF(F204="","",IFERROR(INT(F204-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K204">
+        <f>IF(J204="","",IF(J204&lt;0,"Expired",IF(J204&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L204" t="n">
         <v>1</v>
@@ -12911,13 +12925,13 @@
       <c r="I205" t="n">
         <v>4289</v>
       </c>
-      <c r="J205" t="n">
-        <v>150</v>
-      </c>
-      <c r="K205" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J205">
+        <f>IF(F205="","",IFERROR(INT(F205-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K205">
+        <f>IF(J205="","",IF(J205&lt;0,"Expired",IF(J205&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L205" t="n">
         <v>1</v>
@@ -12972,13 +12986,13 @@
       <c r="I206" t="n">
         <v>4289</v>
       </c>
-      <c r="J206" t="n">
-        <v>150</v>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J206">
+        <f>IF(F206="","",IFERROR(INT(F206-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K206">
+        <f>IF(J206="","",IF(J206&lt;0,"Expired",IF(J206&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L206" t="n">
         <v>1</v>
@@ -13033,13 +13047,13 @@
       <c r="I207" t="n">
         <v>4289</v>
       </c>
-      <c r="J207" t="n">
-        <v>150</v>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J207">
+        <f>IF(F207="","",IFERROR(INT(F207-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K207">
+        <f>IF(J207="","",IF(J207&lt;0,"Expired",IF(J207&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L207" t="n">
         <v>1</v>
@@ -13094,13 +13108,13 @@
       <c r="I208" t="n">
         <v>4289</v>
       </c>
-      <c r="J208" t="n">
-        <v>164</v>
-      </c>
-      <c r="K208" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J208">
+        <f>IF(F208="","",IFERROR(INT(F208-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K208">
+        <f>IF(J208="","",IF(J208&lt;0,"Expired",IF(J208&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L208" t="n">
         <v>1</v>
@@ -13155,13 +13169,13 @@
       <c r="I209" t="n">
         <v>4289</v>
       </c>
-      <c r="J209" t="n">
-        <v>164</v>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J209">
+        <f>IF(F209="","",IFERROR(INT(F209-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K209">
+        <f>IF(J209="","",IF(J209&lt;0,"Expired",IF(J209&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L209" t="n">
         <v>1</v>
@@ -13216,13 +13230,13 @@
       <c r="I210" t="n">
         <v>4289</v>
       </c>
-      <c r="J210" t="n">
-        <v>150</v>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J210">
+        <f>IF(F210="","",IFERROR(INT(F210-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K210">
+        <f>IF(J210="","",IF(J210&lt;0,"Expired",IF(J210&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L210" t="n">
         <v>1</v>
@@ -13277,13 +13291,13 @@
       <c r="I211" t="n">
         <v>4289</v>
       </c>
-      <c r="J211" t="n">
-        <v>164</v>
-      </c>
-      <c r="K211" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J211">
+        <f>IF(F211="","",IFERROR(INT(F211-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K211">
+        <f>IF(J211="","",IF(J211&lt;0,"Expired",IF(J211&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L211" t="n">
         <v>1</v>
@@ -13338,13 +13352,13 @@
       <c r="I212" t="n">
         <v>4289</v>
       </c>
-      <c r="J212" t="n">
-        <v>164</v>
-      </c>
-      <c r="K212" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J212">
+        <f>IF(F212="","",IFERROR(INT(F212-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K212">
+        <f>IF(J212="","",IF(J212&lt;0,"Expired",IF(J212&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L212" t="n">
         <v>1</v>
@@ -13399,13 +13413,13 @@
       <c r="I213" t="n">
         <v>4289</v>
       </c>
-      <c r="J213" t="n">
-        <v>150</v>
-      </c>
-      <c r="K213" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J213">
+        <f>IF(F213="","",IFERROR(INT(F213-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K213">
+        <f>IF(J213="","",IF(J213&lt;0,"Expired",IF(J213&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L213" t="n">
         <v>1</v>
@@ -13460,13 +13474,13 @@
       <c r="I214" t="n">
         <v>4289</v>
       </c>
-      <c r="J214" t="n">
-        <v>164</v>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J214">
+        <f>IF(F214="","",IFERROR(INT(F214-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K214">
+        <f>IF(J214="","",IF(J214&lt;0,"Expired",IF(J214&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L214" t="n">
         <v>1</v>
@@ -13521,13 +13535,13 @@
       <c r="I215" t="n">
         <v>4289</v>
       </c>
-      <c r="J215" t="n">
-        <v>150</v>
-      </c>
-      <c r="K215" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J215">
+        <f>IF(F215="","",IFERROR(INT(F215-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K215">
+        <f>IF(J215="","",IF(J215&lt;0,"Expired",IF(J215&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L215" t="n">
         <v>1</v>
@@ -13582,13 +13596,13 @@
       <c r="I216" t="n">
         <v>4289</v>
       </c>
-      <c r="J216" t="n">
-        <v>164</v>
-      </c>
-      <c r="K216" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J216">
+        <f>IF(F216="","",IFERROR(INT(F216-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K216">
+        <f>IF(J216="","",IF(J216&lt;0,"Expired",IF(J216&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L216" t="n">
         <v>1</v>
@@ -13643,13 +13657,13 @@
       <c r="I217" t="n">
         <v>4289</v>
       </c>
-      <c r="J217" t="n">
-        <v>164</v>
-      </c>
-      <c r="K217" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J217">
+        <f>IF(F217="","",IFERROR(INT(F217-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K217">
+        <f>IF(J217="","",IF(J217&lt;0,"Expired",IF(J217&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L217" t="n">
         <v>1</v>
@@ -13704,13 +13718,13 @@
       <c r="I218" t="n">
         <v>4289</v>
       </c>
-      <c r="J218" t="n">
-        <v>164</v>
-      </c>
-      <c r="K218" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J218">
+        <f>IF(F218="","",IFERROR(INT(F218-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K218">
+        <f>IF(J218="","",IF(J218&lt;0,"Expired",IF(J218&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L218" t="n">
         <v>1</v>
@@ -13765,13 +13779,13 @@
       <c r="I219" t="n">
         <v>4289</v>
       </c>
-      <c r="J219" t="n">
-        <v>164</v>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J219">
+        <f>IF(F219="","",IFERROR(INT(F219-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K219">
+        <f>IF(J219="","",IF(J219&lt;0,"Expired",IF(J219&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L219" t="n">
         <v>1</v>
@@ -13826,13 +13840,13 @@
       <c r="I220" t="n">
         <v>4289</v>
       </c>
-      <c r="J220" t="n">
-        <v>164</v>
-      </c>
-      <c r="K220" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J220">
+        <f>IF(F220="","",IFERROR(INT(F220-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K220">
+        <f>IF(J220="","",IF(J220&lt;0,"Expired",IF(J220&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L220" t="n">
         <v>1</v>
@@ -13887,13 +13901,13 @@
       <c r="I221" t="n">
         <v>4289</v>
       </c>
-      <c r="J221" t="n">
-        <v>164</v>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J221">
+        <f>IF(F221="","",IFERROR(INT(F221-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K221">
+        <f>IF(J221="","",IF(J221&lt;0,"Expired",IF(J221&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L221" t="n">
         <v>1</v>
@@ -13948,13 +13962,13 @@
       <c r="I222" t="n">
         <v>7152</v>
       </c>
-      <c r="J222" t="n">
-        <v>233</v>
-      </c>
-      <c r="K222" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J222">
+        <f>IF(F222="","",IFERROR(INT(F222-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K222">
+        <f>IF(J222="","",IF(J222&lt;0,"Expired",IF(J222&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L222" t="n">
         <v>1</v>
@@ -14009,13 +14023,13 @@
       <c r="I223" t="n">
         <v>7332</v>
       </c>
-      <c r="J223" t="n">
-        <v>40</v>
-      </c>
-      <c r="K223" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J223">
+        <f>IF(F223="","",IFERROR(INT(F223-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K223">
+        <f>IF(J223="","",IF(J223&lt;0,"Expired",IF(J223&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L223" t="n">
         <v>1</v>
@@ -14070,13 +14084,13 @@
       <c r="I224" t="n">
         <v>7332</v>
       </c>
-      <c r="J224" t="n">
-        <v>39</v>
-      </c>
-      <c r="K224" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J224">
+        <f>IF(F224="","",IFERROR(INT(F224-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K224">
+        <f>IF(J224="","",IF(J224&lt;0,"Expired",IF(J224&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L224" t="n">
         <v>1</v>
@@ -14131,13 +14145,13 @@
       <c r="I225" t="n">
         <v>7934</v>
       </c>
-      <c r="J225" t="n">
-        <v>39</v>
-      </c>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J225">
+        <f>IF(F225="","",IFERROR(INT(F225-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K225">
+        <f>IF(J225="","",IF(J225&lt;0,"Expired",IF(J225&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L225" t="n">
         <v>1</v>
@@ -14192,13 +14206,13 @@
       <c r="I226" t="n">
         <v>7332</v>
       </c>
-      <c r="J226" t="n">
-        <v>39</v>
-      </c>
-      <c r="K226" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J226">
+        <f>IF(F226="","",IFERROR(INT(F226-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K226">
+        <f>IF(J226="","",IF(J226&lt;0,"Expired",IF(J226&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L226" t="n">
         <v>1</v>
@@ -14253,13 +14267,13 @@
       <c r="I227" t="n">
         <v>7934</v>
       </c>
-      <c r="J227" t="n">
-        <v>39</v>
-      </c>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J227">
+        <f>IF(F227="","",IFERROR(INT(F227-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K227">
+        <f>IF(J227="","",IF(J227&lt;0,"Expired",IF(J227&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L227" t="n">
         <v>1</v>
@@ -14314,13 +14328,13 @@
       <c r="I228" t="n">
         <v>7332</v>
       </c>
-      <c r="J228" t="n">
-        <v>39</v>
-      </c>
-      <c r="K228" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J228">
+        <f>IF(F228="","",IFERROR(INT(F228-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K228">
+        <f>IF(J228="","",IF(J228&lt;0,"Expired",IF(J228&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L228" t="n">
         <v>1</v>
@@ -14375,13 +14389,13 @@
       <c r="I229" t="n">
         <v>7332</v>
       </c>
-      <c r="J229" t="n">
-        <v>39</v>
-      </c>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J229">
+        <f>IF(F229="","",IFERROR(INT(F229-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K229">
+        <f>IF(J229="","",IF(J229&lt;0,"Expired",IF(J229&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L229" t="n">
         <v>1</v>
@@ -14436,13 +14450,13 @@
       <c r="I230" t="n">
         <v>7447</v>
       </c>
-      <c r="J230" t="n">
-        <v>108</v>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J230">
+        <f>IF(F230="","",IFERROR(INT(F230-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K230">
+        <f>IF(J230="","",IF(J230&lt;0,"Expired",IF(J230&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L230" t="n">
         <v>1</v>
@@ -14497,13 +14511,13 @@
       <c r="I231" t="n">
         <v>6306</v>
       </c>
-      <c r="J231" t="n">
-        <v>337</v>
-      </c>
-      <c r="K231" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J231">
+        <f>IF(F231="","",IFERROR(INT(F231-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K231">
+        <f>IF(J231="","",IF(J231&lt;0,"Expired",IF(J231&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L231" t="n">
         <v>1</v>
@@ -14558,13 +14572,13 @@
       <c r="I232" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J232" t="n">
-        <v>130</v>
-      </c>
-      <c r="K232" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J232">
+        <f>IF(F232="","",IFERROR(INT(F232-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K232">
+        <f>IF(J232="","",IF(J232&lt;0,"Expired",IF(J232&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L232" t="n">
         <v>1</v>
@@ -14619,13 +14633,13 @@
       <c r="I233" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J233" t="n">
-        <v>128</v>
-      </c>
-      <c r="K233" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J233">
+        <f>IF(F233="","",IFERROR(INT(F233-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K233">
+        <f>IF(J233="","",IF(J233&lt;0,"Expired",IF(J233&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L233" t="n">
         <v>1</v>
@@ -14680,13 +14694,13 @@
       <c r="I234" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J234" t="n">
-        <v>128</v>
-      </c>
-      <c r="K234" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J234">
+        <f>IF(F234="","",IFERROR(INT(F234-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K234">
+        <f>IF(J234="","",IF(J234&lt;0,"Expired",IF(J234&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L234" t="n">
         <v>1</v>
@@ -14741,13 +14755,13 @@
       <c r="I235" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J235" t="n">
-        <v>128</v>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J235">
+        <f>IF(F235="","",IFERROR(INT(F235-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K235">
+        <f>IF(J235="","",IF(J235&lt;0,"Expired",IF(J235&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L235" t="n">
         <v>1</v>
@@ -14802,13 +14816,13 @@
       <c r="I236" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J236" t="n">
-        <v>128</v>
-      </c>
-      <c r="K236" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J236">
+        <f>IF(F236="","",IFERROR(INT(F236-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K236">
+        <f>IF(J236="","",IF(J236&lt;0,"Expired",IF(J236&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L236" t="n">
         <v>1</v>
@@ -14863,13 +14877,13 @@
       <c r="I237" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J237" t="n">
-        <v>128</v>
-      </c>
-      <c r="K237" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J237">
+        <f>IF(F237="","",IFERROR(INT(F237-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K237">
+        <f>IF(J237="","",IF(J237&lt;0,"Expired",IF(J237&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L237" t="n">
         <v>1</v>
@@ -14924,13 +14938,13 @@
       <c r="I238" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J238" t="n">
-        <v>128</v>
-      </c>
-      <c r="K238" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J238">
+        <f>IF(F238="","",IFERROR(INT(F238-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K238">
+        <f>IF(J238="","",IF(J238&lt;0,"Expired",IF(J238&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L238" t="n">
         <v>1</v>
@@ -14985,13 +14999,13 @@
       <c r="I239" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J239" t="n">
-        <v>128</v>
-      </c>
-      <c r="K239" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J239">
+        <f>IF(F239="","",IFERROR(INT(F239-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K239">
+        <f>IF(J239="","",IF(J239&lt;0,"Expired",IF(J239&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L239" t="n">
         <v>1</v>
@@ -15046,13 +15060,13 @@
       <c r="I240" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J240" t="n">
-        <v>128</v>
-      </c>
-      <c r="K240" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J240">
+        <f>IF(F240="","",IFERROR(INT(F240-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K240">
+        <f>IF(J240="","",IF(J240&lt;0,"Expired",IF(J240&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L240" t="n">
         <v>1</v>
@@ -15107,13 +15121,13 @@
       <c r="I241" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J241" t="n">
-        <v>128</v>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J241">
+        <f>IF(F241="","",IFERROR(INT(F241-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K241">
+        <f>IF(J241="","",IF(J241&lt;0,"Expired",IF(J241&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L241" t="n">
         <v>1</v>
@@ -15168,13 +15182,13 @@
       <c r="I242" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J242" t="n">
-        <v>128</v>
-      </c>
-      <c r="K242" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J242">
+        <f>IF(F242="","",IFERROR(INT(F242-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K242">
+        <f>IF(J242="","",IF(J242&lt;0,"Expired",IF(J242&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L242" t="n">
         <v>1</v>
@@ -15229,13 +15243,13 @@
       <c r="I243" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J243" t="n">
-        <v>128</v>
-      </c>
-      <c r="K243" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J243">
+        <f>IF(F243="","",IFERROR(INT(F243-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K243">
+        <f>IF(J243="","",IF(J243&lt;0,"Expired",IF(J243&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L243" t="n">
         <v>1</v>
@@ -15290,13 +15304,13 @@
       <c r="I244" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J244" t="n">
-        <v>128</v>
-      </c>
-      <c r="K244" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J244">
+        <f>IF(F244="","",IFERROR(INT(F244-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K244">
+        <f>IF(J244="","",IF(J244&lt;0,"Expired",IF(J244&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L244" t="n">
         <v>1</v>
@@ -15351,13 +15365,13 @@
       <c r="I245" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J245" t="n">
-        <v>128</v>
-      </c>
-      <c r="K245" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J245">
+        <f>IF(F245="","",IFERROR(INT(F245-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K245">
+        <f>IF(J245="","",IF(J245&lt;0,"Expired",IF(J245&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L245" t="n">
         <v>1</v>
@@ -15412,13 +15426,13 @@
       <c r="I246" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J246" t="n">
-        <v>128</v>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J246">
+        <f>IF(F246="","",IFERROR(INT(F246-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K246">
+        <f>IF(J246="","",IF(J246&lt;0,"Expired",IF(J246&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L246" t="n">
         <v>1</v>
@@ -15473,13 +15487,13 @@
       <c r="I247" t="n">
         <v>1030.26</v>
       </c>
-      <c r="J247" t="n">
-        <v>128</v>
-      </c>
-      <c r="K247" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J247">
+        <f>IF(F247="","",IFERROR(INT(F247-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K247">
+        <f>IF(J247="","",IF(J247&lt;0,"Expired",IF(J247&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L247" t="n">
         <v>1</v>
@@ -15534,13 +15548,13 @@
       <c r="I248" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J248" t="n">
-        <v>128</v>
-      </c>
-      <c r="K248" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J248">
+        <f>IF(F248="","",IFERROR(INT(F248-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K248">
+        <f>IF(J248="","",IF(J248&lt;0,"Expired",IF(J248&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L248" t="n">
         <v>1</v>
@@ -15595,13 +15609,13 @@
       <c r="I249" t="n">
         <v>1030.26</v>
       </c>
-      <c r="J249" t="n">
-        <v>128</v>
-      </c>
-      <c r="K249" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J249">
+        <f>IF(F249="","",IFERROR(INT(F249-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K249">
+        <f>IF(J249="","",IF(J249&lt;0,"Expired",IF(J249&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L249" t="n">
         <v>1</v>
@@ -15656,13 +15670,13 @@
       <c r="I250" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J250" t="n">
-        <v>128</v>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J250">
+        <f>IF(F250="","",IFERROR(INT(F250-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K250">
+        <f>IF(J250="","",IF(J250&lt;0,"Expired",IF(J250&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L250" t="n">
         <v>1</v>
@@ -15717,13 +15731,13 @@
       <c r="I251" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J251" t="n">
-        <v>128</v>
-      </c>
-      <c r="K251" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J251">
+        <f>IF(F251="","",IFERROR(INT(F251-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K251">
+        <f>IF(J251="","",IF(J251&lt;0,"Expired",IF(J251&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L251" t="n">
         <v>1</v>
@@ -15778,13 +15792,13 @@
       <c r="I252" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J252" t="n">
-        <v>128</v>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J252">
+        <f>IF(F252="","",IFERROR(INT(F252-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K252">
+        <f>IF(J252="","",IF(J252&lt;0,"Expired",IF(J252&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L252" t="n">
         <v>1</v>
@@ -15839,13 +15853,13 @@
       <c r="I253" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J253" t="n">
-        <v>128</v>
-      </c>
-      <c r="K253" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J253">
+        <f>IF(F253="","",IFERROR(INT(F253-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K253">
+        <f>IF(J253="","",IF(J253&lt;0,"Expired",IF(J253&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L253" t="n">
         <v>1</v>
@@ -15900,13 +15914,13 @@
       <c r="I254" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J254" t="n">
-        <v>128</v>
-      </c>
-      <c r="K254" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J254">
+        <f>IF(F254="","",IFERROR(INT(F254-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K254">
+        <f>IF(J254="","",IF(J254&lt;0,"Expired",IF(J254&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L254" t="n">
         <v>1</v>
@@ -15961,13 +15975,13 @@
       <c r="I255" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J255" t="n">
-        <v>128</v>
-      </c>
-      <c r="K255" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J255">
+        <f>IF(F255="","",IFERROR(INT(F255-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K255">
+        <f>IF(J255="","",IF(J255&lt;0,"Expired",IF(J255&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L255" t="n">
         <v>1</v>
@@ -16022,13 +16036,13 @@
       <c r="I256" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J256" t="n">
-        <v>128</v>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J256">
+        <f>IF(F256="","",IFERROR(INT(F256-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K256">
+        <f>IF(J256="","",IF(J256&lt;0,"Expired",IF(J256&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L256" t="n">
         <v>1</v>
@@ -16083,13 +16097,13 @@
       <c r="I257" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J257" t="n">
-        <v>128</v>
-      </c>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J257">
+        <f>IF(F257="","",IFERROR(INT(F257-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K257">
+        <f>IF(J257="","",IF(J257&lt;0,"Expired",IF(J257&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L257" t="n">
         <v>1</v>
@@ -16144,13 +16158,13 @@
       <c r="I258" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J258" t="n">
-        <v>128</v>
-      </c>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J258">
+        <f>IF(F258="","",IFERROR(INT(F258-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K258">
+        <f>IF(J258="","",IF(J258&lt;0,"Expired",IF(J258&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L258" t="n">
         <v>1</v>
@@ -16205,13 +16219,13 @@
       <c r="I259" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J259" t="n">
-        <v>128</v>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J259">
+        <f>IF(F259="","",IFERROR(INT(F259-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K259">
+        <f>IF(J259="","",IF(J259&lt;0,"Expired",IF(J259&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L259" t="n">
         <v>1</v>
@@ -16266,13 +16280,13 @@
       <c r="I260" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J260" t="n">
-        <v>128</v>
-      </c>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J260">
+        <f>IF(F260="","",IFERROR(INT(F260-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K260">
+        <f>IF(J260="","",IF(J260&lt;0,"Expired",IF(J260&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L260" t="n">
         <v>1</v>
@@ -16327,13 +16341,13 @@
       <c r="I261" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J261" t="n">
-        <v>128</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J261">
+        <f>IF(F261="","",IFERROR(INT(F261-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K261">
+        <f>IF(J261="","",IF(J261&lt;0,"Expired",IF(J261&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L261" t="n">
         <v>1</v>
@@ -16388,13 +16402,13 @@
       <c r="I262" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J262" t="n">
-        <v>128</v>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J262">
+        <f>IF(F262="","",IFERROR(INT(F262-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K262">
+        <f>IF(J262="","",IF(J262&lt;0,"Expired",IF(J262&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L262" t="n">
         <v>1</v>
@@ -16449,13 +16463,13 @@
       <c r="I263" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J263" t="n">
-        <v>128</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J263">
+        <f>IF(F263="","",IFERROR(INT(F263-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K263">
+        <f>IF(J263="","",IF(J263&lt;0,"Expired",IF(J263&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L263" t="n">
         <v>1</v>
@@ -16510,13 +16524,13 @@
       <c r="I264" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J264" t="n">
-        <v>128</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J264">
+        <f>IF(F264="","",IFERROR(INT(F264-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K264">
+        <f>IF(J264="","",IF(J264&lt;0,"Expired",IF(J264&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L264" t="n">
         <v>1</v>
@@ -16571,13 +16585,13 @@
       <c r="I265" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J265" t="n">
-        <v>128</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J265">
+        <f>IF(F265="","",IFERROR(INT(F265-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K265">
+        <f>IF(J265="","",IF(J265&lt;0,"Expired",IF(J265&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L265" t="n">
         <v>1</v>
@@ -16632,13 +16646,13 @@
       <c r="I266" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J266" t="n">
-        <v>128</v>
-      </c>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J266">
+        <f>IF(F266="","",IFERROR(INT(F266-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K266">
+        <f>IF(J266="","",IF(J266&lt;0,"Expired",IF(J266&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L266" t="n">
         <v>1</v>
@@ -16693,13 +16707,13 @@
       <c r="I267" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J267" t="n">
-        <v>128</v>
-      </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J267">
+        <f>IF(F267="","",IFERROR(INT(F267-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K267">
+        <f>IF(J267="","",IF(J267&lt;0,"Expired",IF(J267&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L267" t="n">
         <v>1</v>
@@ -16754,13 +16768,13 @@
       <c r="I268" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J268" t="n">
-        <v>128</v>
-      </c>
-      <c r="K268" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J268">
+        <f>IF(F268="","",IFERROR(INT(F268-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K268">
+        <f>IF(J268="","",IF(J268&lt;0,"Expired",IF(J268&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L268" t="n">
         <v>1</v>
@@ -16815,13 +16829,13 @@
       <c r="I269" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J269" t="n">
-        <v>128</v>
-      </c>
-      <c r="K269" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J269">
+        <f>IF(F269="","",IFERROR(INT(F269-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K269">
+        <f>IF(J269="","",IF(J269&lt;0,"Expired",IF(J269&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L269" t="n">
         <v>1</v>
@@ -16876,13 +16890,13 @@
       <c r="I270" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J270" t="n">
-        <v>128</v>
-      </c>
-      <c r="K270" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J270">
+        <f>IF(F270="","",IFERROR(INT(F270-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K270">
+        <f>IF(J270="","",IF(J270&lt;0,"Expired",IF(J270&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L270" t="n">
         <v>1</v>
@@ -16937,13 +16951,13 @@
       <c r="I271" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J271" t="n">
-        <v>128</v>
-      </c>
-      <c r="K271" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J271">
+        <f>IF(F271="","",IFERROR(INT(F271-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K271">
+        <f>IF(J271="","",IF(J271&lt;0,"Expired",IF(J271&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L271" t="n">
         <v>1</v>
@@ -16998,13 +17012,13 @@
       <c r="I272" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J272" t="n">
-        <v>128</v>
-      </c>
-      <c r="K272" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J272">
+        <f>IF(F272="","",IFERROR(INT(F272-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K272">
+        <f>IF(J272="","",IF(J272&lt;0,"Expired",IF(J272&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L272" t="n">
         <v>1</v>
@@ -17059,13 +17073,13 @@
       <c r="I273" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J273" t="n">
-        <v>128</v>
-      </c>
-      <c r="K273" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J273">
+        <f>IF(F273="","",IFERROR(INT(F273-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K273">
+        <f>IF(J273="","",IF(J273&lt;0,"Expired",IF(J273&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L273" t="n">
         <v>1</v>
@@ -17120,13 +17134,13 @@
       <c r="I274" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J274" t="n">
-        <v>128</v>
-      </c>
-      <c r="K274" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J274">
+        <f>IF(F274="","",IFERROR(INT(F274-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K274">
+        <f>IF(J274="","",IF(J274&lt;0,"Expired",IF(J274&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L274" t="n">
         <v>1</v>
@@ -17181,13 +17195,13 @@
       <c r="I275" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J275" t="n">
-        <v>128</v>
-      </c>
-      <c r="K275" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J275">
+        <f>IF(F275="","",IFERROR(INT(F275-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K275">
+        <f>IF(J275="","",IF(J275&lt;0,"Expired",IF(J275&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L275" t="n">
         <v>1</v>
@@ -17242,13 +17256,13 @@
       <c r="I276" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J276" t="n">
-        <v>128</v>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J276">
+        <f>IF(F276="","",IFERROR(INT(F276-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K276">
+        <f>IF(J276="","",IF(J276&lt;0,"Expired",IF(J276&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L276" t="n">
         <v>1</v>
@@ -17303,13 +17317,13 @@
       <c r="I277" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J277" t="n">
-        <v>128</v>
-      </c>
-      <c r="K277" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J277">
+        <f>IF(F277="","",IFERROR(INT(F277-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K277">
+        <f>IF(J277="","",IF(J277&lt;0,"Expired",IF(J277&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L277" t="n">
         <v>1</v>
@@ -17364,13 +17378,13 @@
       <c r="I278" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J278" t="n">
-        <v>128</v>
-      </c>
-      <c r="K278" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J278">
+        <f>IF(F278="","",IFERROR(INT(F278-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K278">
+        <f>IF(J278="","",IF(J278&lt;0,"Expired",IF(J278&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L278" t="n">
         <v>1</v>
@@ -17425,13 +17439,13 @@
       <c r="I279" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J279" t="n">
-        <v>128</v>
-      </c>
-      <c r="K279" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J279">
+        <f>IF(F279="","",IFERROR(INT(F279-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K279">
+        <f>IF(J279="","",IF(J279&lt;0,"Expired",IF(J279&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L279" t="n">
         <v>1</v>
@@ -17486,13 +17500,13 @@
       <c r="I280" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J280" t="n">
-        <v>128</v>
-      </c>
-      <c r="K280" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J280">
+        <f>IF(F280="","",IFERROR(INT(F280-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K280">
+        <f>IF(J280="","",IF(J280&lt;0,"Expired",IF(J280&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L280" t="n">
         <v>1</v>
@@ -17547,13 +17561,13 @@
       <c r="I281" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J281" t="n">
-        <v>128</v>
-      </c>
-      <c r="K281" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J281">
+        <f>IF(F281="","",IFERROR(INT(F281-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K281">
+        <f>IF(J281="","",IF(J281&lt;0,"Expired",IF(J281&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L281" t="n">
         <v>1</v>
@@ -17608,13 +17622,13 @@
       <c r="I282" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J282" t="n">
-        <v>128</v>
-      </c>
-      <c r="K282" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J282">
+        <f>IF(F282="","",IFERROR(INT(F282-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K282">
+        <f>IF(J282="","",IF(J282&lt;0,"Expired",IF(J282&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L282" t="n">
         <v>1</v>
@@ -17669,13 +17683,13 @@
       <c r="I283" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J283" t="n">
-        <v>128</v>
-      </c>
-      <c r="K283" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J283">
+        <f>IF(F283="","",IFERROR(INT(F283-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K283">
+        <f>IF(J283="","",IF(J283&lt;0,"Expired",IF(J283&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L283" t="n">
         <v>1</v>
@@ -17730,13 +17744,13 @@
       <c r="I284" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J284" t="n">
-        <v>128</v>
-      </c>
-      <c r="K284" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J284">
+        <f>IF(F284="","",IFERROR(INT(F284-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K284">
+        <f>IF(J284="","",IF(J284&lt;0,"Expired",IF(J284&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L284" t="n">
         <v>1</v>
@@ -17791,13 +17805,13 @@
       <c r="I285" t="n">
         <v>772.5599999999999</v>
       </c>
-      <c r="J285" t="n">
-        <v>128</v>
-      </c>
-      <c r="K285" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J285">
+        <f>IF(F285="","",IFERROR(INT(F285-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K285">
+        <f>IF(J285="","",IF(J285&lt;0,"Expired",IF(J285&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L285" t="n">
         <v>1</v>
@@ -17852,13 +17866,13 @@
       <c r="I286" t="n">
         <v>1030.26</v>
       </c>
-      <c r="J286" t="n">
-        <v>128</v>
-      </c>
-      <c r="K286" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J286">
+        <f>IF(F286="","",IFERROR(INT(F286-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K286">
+        <f>IF(J286="","",IF(J286&lt;0,"Expired",IF(J286&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L286" t="n">
         <v>1</v>
@@ -17913,13 +17927,13 @@
       <c r="I287" t="n">
         <v>6721</v>
       </c>
-      <c r="J287" t="n">
-        <v>113</v>
-      </c>
-      <c r="K287" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J287">
+        <f>IF(F287="","",IFERROR(INT(F287-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K287">
+        <f>IF(J287="","",IF(J287&lt;0,"Expired",IF(J287&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L287" t="n">
         <v>1</v>
@@ -17974,13 +17988,13 @@
       <c r="I288" t="n">
         <v>670</v>
       </c>
-      <c r="J288" t="n">
-        <v>326</v>
-      </c>
-      <c r="K288" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J288">
+        <f>IF(F288="","",IFERROR(INT(F288-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K288">
+        <f>IF(J288="","",IF(J288&lt;0,"Expired",IF(J288&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L288" t="n">
         <v>1</v>
@@ -18035,13 +18049,13 @@
       <c r="I289" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J289" t="n">
-        <v>30</v>
-      </c>
-      <c r="K289" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J289">
+        <f>IF(F289="","",IFERROR(INT(F289-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K289">
+        <f>IF(J289="","",IF(J289&lt;0,"Expired",IF(J289&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L289" t="n">
         <v>1</v>
@@ -18096,13 +18110,13 @@
       <c r="I290" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J290" t="n">
-        <v>30</v>
-      </c>
-      <c r="K290" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J290">
+        <f>IF(F290="","",IFERROR(INT(F290-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K290">
+        <f>IF(J290="","",IF(J290&lt;0,"Expired",IF(J290&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L290" t="n">
         <v>1</v>
@@ -18157,13 +18171,13 @@
       <c r="I291" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J291" t="n">
-        <v>29</v>
-      </c>
-      <c r="K291" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J291">
+        <f>IF(F291="","",IFERROR(INT(F291-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K291">
+        <f>IF(J291="","",IF(J291&lt;0,"Expired",IF(J291&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L291" t="n">
         <v>1</v>
@@ -18218,13 +18232,13 @@
       <c r="I292" t="n">
         <v>2115.93</v>
       </c>
-      <c r="J292" t="n">
-        <v>30</v>
-      </c>
-      <c r="K292" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J292">
+        <f>IF(F292="","",IFERROR(INT(F292-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K292">
+        <f>IF(J292="","",IF(J292&lt;0,"Expired",IF(J292&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L292" t="n">
         <v>1</v>
@@ -18279,13 +18293,13 @@
       <c r="I293" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J293" t="n">
-        <v>30</v>
-      </c>
-      <c r="K293" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J293">
+        <f>IF(F293="","",IFERROR(INT(F293-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K293">
+        <f>IF(J293="","",IF(J293&lt;0,"Expired",IF(J293&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L293" t="n">
         <v>1</v>
@@ -18340,13 +18354,13 @@
       <c r="I294" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J294" t="n">
-        <v>30</v>
-      </c>
-      <c r="K294" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J294">
+        <f>IF(F294="","",IFERROR(INT(F294-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K294">
+        <f>IF(J294="","",IF(J294&lt;0,"Expired",IF(J294&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L294" t="n">
         <v>1</v>
@@ -18401,13 +18415,13 @@
       <c r="I295" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J295" t="n">
-        <v>30</v>
-      </c>
-      <c r="K295" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J295">
+        <f>IF(F295="","",IFERROR(INT(F295-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K295">
+        <f>IF(J295="","",IF(J295&lt;0,"Expired",IF(J295&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L295" t="n">
         <v>1</v>
@@ -18462,13 +18476,13 @@
       <c r="I296" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J296" t="n">
-        <v>30</v>
-      </c>
-      <c r="K296" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J296">
+        <f>IF(F296="","",IFERROR(INT(F296-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K296">
+        <f>IF(J296="","",IF(J296&lt;0,"Expired",IF(J296&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L296" t="n">
         <v>1</v>
@@ -18523,13 +18537,13 @@
       <c r="I297" t="n">
         <v>1834.29</v>
       </c>
-      <c r="J297" t="n">
-        <v>30</v>
-      </c>
-      <c r="K297" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J297">
+        <f>IF(F297="","",IFERROR(INT(F297-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K297">
+        <f>IF(J297="","",IF(J297&lt;0,"Expired",IF(J297&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L297" t="n">
         <v>1</v>
@@ -18584,13 +18598,13 @@
       <c r="I298" t="n">
         <v>31370</v>
       </c>
-      <c r="J298" t="n">
-        <v>124</v>
-      </c>
-      <c r="K298" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J298">
+        <f>IF(F298="","",IFERROR(INT(F298-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K298">
+        <f>IF(J298="","",IF(J298&lt;0,"Expired",IF(J298&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L298" t="n">
         <v>1</v>
@@ -18645,13 +18659,13 @@
       <c r="I299" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J299" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K299" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J299">
+        <f>IF(F299="","",IFERROR(INT(F299-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K299">
+        <f>IF(J299="","",IF(J299&lt;0,"Expired",IF(J299&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L299" t="n">
         <v>5</v>
@@ -18706,13 +18720,13 @@
       <c r="I300" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J300" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K300" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J300">
+        <f>IF(F300="","",IFERROR(INT(F300-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K300">
+        <f>IF(J300="","",IF(J300&lt;0,"Expired",IF(J300&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L300" t="n">
         <v>5</v>
@@ -18767,13 +18781,13 @@
       <c r="I301" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J301" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K301" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J301">
+        <f>IF(F301="","",IFERROR(INT(F301-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K301">
+        <f>IF(J301="","",IF(J301&lt;0,"Expired",IF(J301&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L301" t="n">
         <v>5</v>
@@ -18828,13 +18842,13 @@
       <c r="I302" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J302" t="n">
-        <v>24</v>
-      </c>
-      <c r="K302" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J302">
+        <f>IF(F302="","",IFERROR(INT(F302-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K302">
+        <f>IF(J302="","",IF(J302&lt;0,"Expired",IF(J302&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L302" t="n">
         <v>1</v>
@@ -18889,13 +18903,13 @@
       <c r="I303" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J303" t="n">
-        <v>24</v>
-      </c>
-      <c r="K303" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J303">
+        <f>IF(F303="","",IFERROR(INT(F303-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K303">
+        <f>IF(J303="","",IF(J303&lt;0,"Expired",IF(J303&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L303" t="n">
         <v>1</v>
@@ -18950,13 +18964,13 @@
       <c r="I304" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J304" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K304" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J304">
+        <f>IF(F304="","",IFERROR(INT(F304-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K304">
+        <f>IF(J304="","",IF(J304&lt;0,"Expired",IF(J304&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L304" t="n">
         <v>5</v>
@@ -19011,13 +19025,13 @@
       <c r="I305" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J305" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K305" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J305">
+        <f>IF(F305="","",IFERROR(INT(F305-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K305">
+        <f>IF(J305="","",IF(J305&lt;0,"Expired",IF(J305&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L305" t="n">
         <v>5</v>
@@ -19072,13 +19086,13 @@
       <c r="I306" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J306" t="n">
-        <v>24</v>
-      </c>
-      <c r="K306" t="inlineStr">
-        <is>
-          <t>Expiring Soon</t>
-        </is>
+      <c r="J306">
+        <f>IF(F306="","",IFERROR(INT(F306-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K306">
+        <f>IF(J306="","",IF(J306&lt;0,"Expired",IF(J306&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L306" t="n">
         <v>1</v>
@@ -19133,13 +19147,13 @@
       <c r="I307" t="n">
         <v>6166.7</v>
       </c>
-      <c r="J307" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K307" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J307">
+        <f>IF(F307="","",IFERROR(INT(F307-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K307">
+        <f>IF(J307="","",IF(J307&lt;0,"Expired",IF(J307&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L307" t="n">
         <v>5</v>
@@ -19194,13 +19208,13 @@
       <c r="I308" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J308" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K308" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J308">
+        <f>IF(F308="","",IFERROR(INT(F308-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K308">
+        <f>IF(J308="","",IF(J308&lt;0,"Expired",IF(J308&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L308" t="n">
         <v>5</v>
@@ -19255,13 +19269,13 @@
       <c r="I309" t="n">
         <v>5226.02</v>
       </c>
-      <c r="J309" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K309" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J309">
+        <f>IF(F309="","",IFERROR(INT(F309-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K309">
+        <f>IF(J309="","",IF(J309&lt;0,"Expired",IF(J309&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L309" t="n">
         <v>5</v>
@@ -19316,13 +19330,13 @@
       <c r="I310" t="n">
         <v>6166.7</v>
       </c>
-      <c r="J310" t="n">
-        <v>1485</v>
-      </c>
-      <c r="K310" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J310">
+        <f>IF(F310="","",IFERROR(INT(F310-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K310">
+        <f>IF(J310="","",IF(J310&lt;0,"Expired",IF(J310&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L310" t="n">
         <v>5</v>
@@ -19377,13 +19391,13 @@
       <c r="I311" t="n">
         <v>33650</v>
       </c>
-      <c r="J311" t="n">
-        <v>252</v>
-      </c>
-      <c r="K311" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J311">
+        <f>IF(F311="","",IFERROR(INT(F311-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K311">
+        <f>IF(J311="","",IF(J311&lt;0,"Expired",IF(J311&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L311" t="n">
         <v>1</v>
@@ -19438,13 +19452,13 @@
       <c r="I312" t="n">
         <v>6973</v>
       </c>
-      <c r="J312" t="n">
-        <v>204</v>
-      </c>
-      <c r="K312" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J312">
+        <f>IF(F312="","",IFERROR(INT(F312-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K312">
+        <f>IF(J312="","",IF(J312&lt;0,"Expired",IF(J312&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L312" t="n">
         <v>1</v>
@@ -19499,13 +19513,13 @@
       <c r="I313" t="n">
         <v>6664</v>
       </c>
-      <c r="J313" t="n">
-        <v>170</v>
-      </c>
-      <c r="K313" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J313">
+        <f>IF(F313="","",IFERROR(INT(F313-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K313">
+        <f>IF(J313="","",IF(J313&lt;0,"Expired",IF(J313&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L313" t="n">
         <v>1</v>
@@ -19560,13 +19574,13 @@
       <c r="I314" t="n">
         <v>6346</v>
       </c>
-      <c r="J314" t="n">
-        <v>256</v>
-      </c>
-      <c r="K314" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J314">
+        <f>IF(F314="","",IFERROR(INT(F314-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K314">
+        <f>IF(J314="","",IF(J314&lt;0,"Expired",IF(J314&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L314" t="n">
         <v>1</v>
@@ -19621,13 +19635,13 @@
       <c r="I315" t="n">
         <v>6346</v>
       </c>
-      <c r="J315" t="n">
-        <v>256</v>
-      </c>
-      <c r="K315" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J315">
+        <f>IF(F315="","",IFERROR(INT(F315-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K315">
+        <f>IF(J315="","",IF(J315&lt;0,"Expired",IF(J315&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L315" t="n">
         <v>1</v>
@@ -19682,13 +19696,13 @@
       <c r="I316" t="n">
         <v>6346</v>
       </c>
-      <c r="J316" t="n">
-        <v>256</v>
-      </c>
-      <c r="K316" t="inlineStr">
-        <is>
-          <t>Active</t>
-        </is>
+      <c r="J316">
+        <f>IF(F316="","",IFERROR(INT(F316-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K316">
+        <f>IF(J316="","",IF(J316&lt;0,"Expired",IF(J316&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
       </c>
       <c r="L316" t="n">
         <v>1</v>
@@ -19700,6 +19714,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M316"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19825,7 +19840,7 @@
         <v>6990</v>
       </c>
       <c r="J2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -19886,7 +19901,7 @@
         <v>5226.02</v>
       </c>
       <c r="J3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -19947,7 +19962,7 @@
         <v>5226.02</v>
       </c>
       <c r="J4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -20008,7 +20023,7 @@
         <v>5226.02</v>
       </c>
       <c r="J5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -20069,7 +20084,7 @@
         <v>1834.29</v>
       </c>
       <c r="J6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -20130,7 +20145,7 @@
         <v>1834.29</v>
       </c>
       <c r="J7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -20191,7 +20206,7 @@
         <v>1834.29</v>
       </c>
       <c r="J8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
@@ -20252,7 +20267,7 @@
         <v>2115.93</v>
       </c>
       <c r="J9" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -20313,7 +20328,7 @@
         <v>1834.29</v>
       </c>
       <c r="J10" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -20374,7 +20389,7 @@
         <v>1834.29</v>
       </c>
       <c r="J11" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -20435,7 +20450,7 @@
         <v>1834.29</v>
       </c>
       <c r="J12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -20496,7 +20511,7 @@
         <v>1834.29</v>
       </c>
       <c r="J13" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -20557,7 +20572,7 @@
         <v>1834.29</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>

--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="📊 Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="All Policies" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Expiry Alerts (&lt;=30d)" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="By Status" sheetId="4" state="visible" r:id="rId4"/>
@@ -338,10 +338,6 @@
             </numRef>
           </val>
         </ser>
-        <dLbls>
-          <showCatName val="1"/>
-          <showPercent val="1"/>
-        </dLbls>
         <firstSliceAng val="0"/>
       </pieChart>
     </plotArea>

--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -20479,12 +20479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109.pdf</t>
+          <t>P6DED152PDA000120.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109</t>
+          <t>P6DED152PDA000120</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D202160528</t>
+          <t>D202160551</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20540,12 +20540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P6DED152PDA000112.pdf</t>
+          <t>P6DED152PDA000109.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P6DED152PDA000112</t>
+          <t>P6DED152PDA000109</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D202160533</t>
+          <t>D202160528</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -20601,12 +20601,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120.pdf</t>
+          <t>P6DED152PDA000112.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120</t>
+          <t>P6DED152PDA000112</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D202160551</t>
+          <t>D202160533</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -20723,12 +20723,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404.pdf</t>
+          <t>P56HFFA0HZK014503.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404</t>
+          <t>P56HFFA0HZK014503</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D202570678 / 15052025</t>
+          <t>D202570760</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -20762,7 +20762,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1834.29</v>
+        <v>2115.93</v>
       </c>
       <c r="J7" t="n">
         <v>28</v>
@@ -20784,12 +20784,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014464.pdf</t>
+          <t>P56HFFA0HZK014404.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014464</t>
+          <t>P56HFFA0HZK014404</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>D202570839</t>
+          <t>D202570678 / 15052025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -20845,12 +20845,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503.pdf</t>
+          <t>P56HFFA0HZK014464.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503</t>
+          <t>P56HFFA0HZK014464</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>D202570760</t>
+          <t>D202570839</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2115.93</v>
+        <v>1834.29</v>
       </c>
       <c r="J9" t="n">
         <v>28</v>
@@ -20906,12 +20906,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507.pdf</t>
+          <t>P56HFFA0ZZK014550.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507</t>
+          <t>P56HFFA0ZZK014550</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D202570869 / 15052025</t>
+          <t>D202570928 / 15052025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -21028,12 +21028,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550.pdf</t>
+          <t>P56HFFA0HZK014507.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550</t>
+          <t>P56HFFA0HZK014507</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>D202570928 / 15052025</t>
+          <t>D202570869 / 15052025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -21089,12 +21089,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553.pdf</t>
+          <t>P56HFFA0ZZK014670.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553</t>
+          <t>P56HFFA0ZZK014670</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>D202570954 / 15052025</t>
+          <t>D202570964 / 15052025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -21150,12 +21150,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670.pdf</t>
+          <t>P56HFFA0ZZK014553.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670</t>
+          <t>P56HFFA0ZZK014553</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>D202570964 / 15052025</t>
+          <t>D202570954 / 15052025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">

--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -20479,12 +20479,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120.pdf</t>
+          <t>P6DED152PDA000109.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120</t>
+          <t>P6DED152PDA000109</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -20494,7 +20494,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D202160551</t>
+          <t>D202160528</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20540,12 +20540,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109.pdf</t>
+          <t>P6DED152PDA000112.pdf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109</t>
+          <t>P6DED152PDA000112</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -20555,7 +20555,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>D202160528</t>
+          <t>D202160533</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -20601,12 +20601,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000112.pdf</t>
+          <t>P6DED152PDA000120.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000112</t>
+          <t>P6DED152PDA000120</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20616,7 +20616,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D202160533</t>
+          <t>D202160551</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -20723,12 +20723,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503.pdf</t>
+          <t>P56HFFA0HZK014404.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503</t>
+          <t>P56HFFA0HZK014404</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20738,7 +20738,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D202570760</t>
+          <t>D202570678 / 15052025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -20762,7 +20762,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2115.93</v>
+        <v>1834.29</v>
       </c>
       <c r="J7" t="n">
         <v>28</v>
@@ -20784,12 +20784,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404.pdf</t>
+          <t>P56HFFA0HZK014464.pdf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404</t>
+          <t>P56HFFA0HZK014464</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -20799,7 +20799,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>D202570678 / 15052025</t>
+          <t>D202570839</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -20845,12 +20845,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014464.pdf</t>
+          <t>P56HFFA0HZK014503.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014464</t>
+          <t>P56HFFA0HZK014503</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20860,7 +20860,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>D202570839</t>
+          <t>D202570760</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20884,7 +20884,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1834.29</v>
+        <v>2115.93</v>
       </c>
       <c r="J9" t="n">
         <v>28</v>
@@ -20906,12 +20906,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550.pdf</t>
+          <t>P56HFFA0HZK014507.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550</t>
+          <t>P56HFFA0HZK014507</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20921,7 +20921,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D202570928 / 15052025</t>
+          <t>D202570869 / 15052025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -21028,12 +21028,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507.pdf</t>
+          <t>P56HFFA0ZZK014550.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507</t>
+          <t>P56HFFA0ZZK014550</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>D202570869 / 15052025</t>
+          <t>D202570928 / 15052025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -21089,12 +21089,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670.pdf</t>
+          <t>P56HFFA0ZZK014553.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670</t>
+          <t>P56HFFA0ZZK014553</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -21104,7 +21104,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>D202570964 / 15052025</t>
+          <t>D202570954 / 15052025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -21150,12 +21150,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553.pdf</t>
+          <t>P56HFFA0ZZK014670.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553</t>
+          <t>P56HFFA0ZZK014670</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>D202570954 / 15052025</t>
+          <t>D202570964 / 15052025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">

--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Policies'!$A$1:$M$316</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Expiry Alerts (&lt;=30d)'!$A$1:$M$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Expiry Alerts (&lt;=30d)'!$A$1:$M$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'By Status'!$A$1:$C$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'By Insurer'!$A$1:$D$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'By Policy Type'!$A$1:$D$3</definedName>
@@ -989,12 +989,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>301</t>
         </is>
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -20345,7 +20345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21208,8 +21208,69 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MD9EMHDL24E217023.pdf</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>MD9EMHDL24E217023</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Royal Sundaram General Insurance Co. Limited</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VGC1159762000101</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>accident, fire, explosion, self-ignition, lightning, theft, burglary, flood, cyclone, storm, earthquake, landslide, riot, strike, terrorism, malicious act, transit</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7934</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Expiring Soon</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Annual</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M14"/>
+  <autoFilter ref="A1:M15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21247,10 +21308,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C2" t="n">
-        <v>1404163</v>
+        <v>1396229</v>
       </c>
     </row>
     <row r="3">
@@ -21260,10 +21321,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
-        <v>39458.31</v>
+        <v>47392.31</v>
       </c>
     </row>
   </sheetData>

--- a/data/extracted.xlsx
+++ b/data/extracted.xlsx
@@ -16,12 +16,12 @@
     <sheet name="By Expiry Month" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Policies'!$A$1:$M$316</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'All Policies'!$A$1:$M$317</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Expiry Alerts (&lt;=30d)'!$A$1:$M$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'By Status'!$A$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'By Insurer'!$A$1:$D$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'By Policy Type'!$A$1:$D$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'By Expiry Month'!$A$1:$B$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'By Status'!$A$1:$C$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'By Insurer'!$A$1:$D$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'By Policy Type'!$A$1:$D$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'By Expiry Month'!$A$1:$B$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -329,12 +329,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'By Status'!$A$2:$A$3</f>
+              <f>'By Status'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'By Status'!$B$2:$B$3</f>
+              <f>'By Status'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -498,12 +498,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'By Expiry Month'!$A$2:$A$14</f>
+              <f>'By Expiry Month'!$A$2:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'By Expiry Month'!$B$2:$B$14</f>
+              <f>'By Expiry Month'!$B$2:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -984,7 +984,7 @@
     <row r="6" ht="40" customHeight="1">
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>316</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M316"/>
+  <dimension ref="A1:M317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20322,9 +20322,34 @@
         </is>
       </c>
     </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Quectel_EC200U&amp;EG915U_Series_AT_Commands_Manual_V1.0-1.pdf</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr"/>
+      <c r="C317" t="inlineStr"/>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr"/>
+      <c r="H317" t="inlineStr"/>
+      <c r="I317" t="inlineStr"/>
+      <c r="J317">
+        <f>IF(F317="","",IFERROR(INT(F317-TODAY()),""))</f>
+        <v/>
+      </c>
+      <c r="K317">
+        <f>IF(J317="","",IF(J317&lt;0,"Expired",IF(J317&lt;=30,"Expiring Soon","Active")))</f>
+        <v/>
+      </c>
+      <c r="L317" t="inlineStr"/>
+      <c r="M317" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M316"/>
-  <conditionalFormatting sqref="K2:K316">
+  <autoFilter ref="A1:M317"/>
+  <conditionalFormatting sqref="K2:K317">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"Active"</formula>
     </cfRule>
@@ -20479,12 +20504,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109.pdf</t>
+          <t>P6DED152PDA000120.pdf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P6DED152PDA000109</t>
+          <t>P6DED152PDA000120</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -20494,7 +20519,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>D202160528</t>
+          <t>D202160551</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -20601,12 +20626,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120.pdf</t>
+          <t>P6DED152PDA000109.pdf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P6DED152PDA000120</t>
+          <t>P6DED152PDA000109</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -20616,7 +20641,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D202160551</t>
+          <t>D202160528</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -20723,12 +20748,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404.pdf</t>
+          <t>P56HFFA0HZK014507.pdf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014404</t>
+          <t>P56HFFA0HZK014507</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -20738,7 +20763,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D202570678 / 15052025</t>
+          <t>D202570869 / 15052025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -20845,12 +20870,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503.pdf</t>
+          <t>P56HFFA0HZK014404.pdf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014503</t>
+          <t>P56HFFA0HZK014404</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -20860,7 +20885,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>D202570760</t>
+          <t>D202570678 / 15052025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -20884,7 +20909,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2115.93</v>
+        <v>1834.29</v>
       </c>
       <c r="J9" t="n">
         <v>28</v>
@@ -20906,12 +20931,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507.pdf</t>
+          <t>P56HFFA0ZZK014670.pdf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P56HFFA0HZK014507</t>
+          <t>P56HFFA0ZZK014670</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -20921,7 +20946,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>D202570869 / 15052025</t>
+          <t>D202570964 / 15052025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -21028,12 +21053,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550.pdf</t>
+          <t>P56HFFA0HZK014503.pdf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014550</t>
+          <t>P56HFFA0HZK014503</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -21043,7 +21068,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>D202570928 / 15052025</t>
+          <t>D202570760</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -21067,7 +21092,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1834.29</v>
+        <v>2115.93</v>
       </c>
       <c r="J12" t="n">
         <v>28</v>
@@ -21089,12 +21114,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553.pdf</t>
+          <t>P56HFFA0ZZK014550.pdf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014553</t>
+          <t>P56HFFA0ZZK014550</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -21104,7 +21129,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>D202570954 / 15052025</t>
+          <t>D202570928 / 15052025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -21150,12 +21175,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670.pdf</t>
+          <t>P56HFFA0ZZK014553.pdf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P56HFFA0ZZK014670</t>
+          <t>P56HFFA0ZZK014553</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -21165,7 +21190,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>D202570964 / 15052025</t>
+          <t>D202570954 / 15052025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -21281,7 +21306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21327,8 +21352,21 @@
         <v>47392.31</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C3"/>
+  <autoFilter ref="A1:C4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21339,7 +21377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21492,8 +21530,18 @@
         <v>6990</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D9"/>
+  <autoFilter ref="A1:D10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21504,7 +21552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21561,8 +21609,18 @@
         <v>48915.54</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D3"/>
+  <autoFilter ref="A1:D4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -21573,7 +21631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21718,8 +21776,14 @@
         <v>9</v>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B14"/>
+  <autoFilter ref="A1:B15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>